--- a/excels/单位表.xlsx
+++ b/excels/单位表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17230"/>
+    <workbookView windowWidth="15350" windowHeight="24880"/>
   </bookViews>
   <sheets>
     <sheet name="custom_units" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="266">
   <si>
     <t>主键</t>
   </si>
@@ -416,7 +416,31 @@
 </t>
   </si>
   <si>
-    <t>崔丝塔娜</t>
+    <t>windrunner</t>
+  </si>
+  <si>
+    <t>models/heroes/windrunner/windrunner.vmdl</t>
+  </si>
+  <si>
+    <t>particles/units/heroes/hero_windrunner\windrunner_base_attack.vpcf</t>
+  </si>
+  <si>
+    <t>Hero_Windrunner</t>
+  </si>
+  <si>
+    <t>soundevents/game_sounds_heroes/game_sounds_windrunner.vsndevts</t>
+  </si>
+  <si>
+    <t>windrunner_powershot</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_RANGED_ATTACK</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_MOVE_GROUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 格雷福斯</t>
   </si>
   <si>
     <t>models/heroes/</t>
@@ -426,15 +450,6 @@
   </si>
   <si>
     <t>soundevents/</t>
-  </si>
-  <si>
-    <t>DOTA_UNIT_CAP_RANGED_ATTACK</t>
-  </si>
-  <si>
-    <t>DOTA_UNIT_CAP_MOVE_GROUND</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 格雷福斯</t>
   </si>
   <si>
     <t xml:space="preserve"> 卢锡安</t>
@@ -835,7 +850,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -867,13 +882,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1035,7 +1043,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1188,12 +1196,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1207,12 +1209,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1248,19 +1244,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1303,12 +1287,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1471,82 +1449,88 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1555,53 +1539,47 @@
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1698,15 +1676,15 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1723,40 +1701,34 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1768,13 +1740,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2207,121 +2176,121 @@
       <c r="J1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="K1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="L1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="M1" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="54" t="s">
+      <c r="N1" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="54" t="s">
+      <c r="O1" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="54" t="s">
+      <c r="P1" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="54" t="s">
+      <c r="Q1" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="54" t="s">
+      <c r="R1" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="S1" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="54" t="s">
+      <c r="T1" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="54" t="s">
+      <c r="U1" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="54" t="s">
+      <c r="V1" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="54" t="s">
+      <c r="W1" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="54" t="s">
+      <c r="X1" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="54" t="s">
+      <c r="Y1" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="54" t="s">
+      <c r="Z1" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="56" t="s">
+      <c r="AA1" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="56" t="s">
+      <c r="AB1" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="54" t="s">
+      <c r="AC1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="54" t="s">
+      <c r="AD1" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="54" t="s">
+      <c r="AE1" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="54" t="s">
+      <c r="AF1" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="54" t="s">
+      <c r="AG1" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="59" t="s">
+      <c r="AH1" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="59" t="s">
+      <c r="AI1" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="59" t="s">
+      <c r="AJ1" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="59" t="s">
+      <c r="AK1" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="60" t="s">
+      <c r="AL1" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="60" t="s">
+      <c r="AM1" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="60" t="s">
+      <c r="AN1" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="60" t="s">
+      <c r="AO1" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="64" t="s">
+      <c r="AP1" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="64" t="s">
+      <c r="AQ1" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="AR1" s="64" t="s">
+      <c r="AR1" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="64" t="s">
+      <c r="AS1" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="64" t="s">
+      <c r="AT1" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="64" t="s">
+      <c r="AU1" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="64" t="s">
+      <c r="AV1" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="64" t="s">
+      <c r="AW1" s="62" t="s">
         <v>47</v>
       </c>
       <c r="AX1" s="49" t="s">
@@ -2339,7 +2308,7 @@
       <c r="BB1" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="BC1" s="66" t="s">
+      <c r="BC1" s="50" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2374,121 +2343,121 @@
       <c r="J2" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="54" t="s">
+      <c r="L2" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="54" t="s">
+      <c r="M2" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="O2" s="54" t="s">
+      <c r="O2" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="P2" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="Q2" s="54" t="s">
+      <c r="Q2" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="R2" s="54" t="s">
+      <c r="R2" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="54" t="s">
+      <c r="S2" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="T2" s="54" t="s">
+      <c r="T2" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="U2" s="54" t="s">
+      <c r="U2" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="V2" s="54" t="s">
+      <c r="V2" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="W2" s="54" t="s">
+      <c r="W2" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="X2" s="54" t="s">
+      <c r="X2" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="Y2" s="54" t="s">
+      <c r="Y2" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="Z2" s="54" t="s">
+      <c r="Z2" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="AA2" s="56" t="s">
+      <c r="AA2" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="AB2" s="56" t="s">
+      <c r="AB2" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="AC2" s="54" t="s">
+      <c r="AC2" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="AD2" s="54" t="s">
+      <c r="AD2" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="AE2" s="54" t="s">
+      <c r="AE2" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="AF2" s="54" t="s">
+      <c r="AF2" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="AG2" s="54" t="s">
+      <c r="AG2" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="AH2" s="59" t="s">
+      <c r="AH2" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="AI2" s="59" t="s">
+      <c r="AI2" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="AJ2" s="59" t="s">
+      <c r="AJ2" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="AK2" s="59" t="s">
+      <c r="AK2" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="AL2" s="60" t="s">
+      <c r="AL2" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="AM2" s="60" t="s">
+      <c r="AM2" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="AN2" s="60" t="s">
+      <c r="AN2" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="AO2" s="60" t="s">
+      <c r="AO2" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="AP2" s="64" t="s">
+      <c r="AP2" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="AQ2" s="64" t="s">
+      <c r="AQ2" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="AR2" s="64" t="s">
+      <c r="AR2" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="AS2" s="64" t="s">
+      <c r="AS2" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="AT2" s="64" t="s">
+      <c r="AT2" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="AU2" s="64" t="s">
+      <c r="AU2" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="AV2" s="64" t="s">
+      <c r="AV2" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="AW2" s="64" t="s">
+      <c r="AW2" s="62" t="s">
         <v>100</v>
       </c>
       <c r="AX2" s="49" t="s">
@@ -2506,7 +2475,7 @@
       <c r="BB2" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="BC2" s="66" t="s">
+      <c r="BC2" s="50" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2520,10 +2489,10 @@
       <c r="C3" s="51">
         <v>1</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="41" t="s">
         <v>109</v>
       </c>
       <c r="F3" s="48">
@@ -2535,103 +2504,103 @@
       <c r="H3" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="41" t="s">
         <v>111</v>
       </c>
       <c r="J3" s="51">
         <v>1</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="55"/>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="55" t="s">
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54"/>
+      <c r="Z3" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="AA3" s="57">
+      <c r="AA3" s="56">
         <v>0</v>
       </c>
-      <c r="AB3" s="57">
+      <c r="AB3" s="56">
         <v>0</v>
       </c>
-      <c r="AC3" s="55">
+      <c r="AC3" s="54">
         <v>500</v>
       </c>
-      <c r="AD3" s="55">
+      <c r="AD3" s="54">
         <v>0</v>
       </c>
-      <c r="AE3" s="55">
+      <c r="AE3" s="54">
         <v>100</v>
       </c>
-      <c r="AF3" s="58">
+      <c r="AF3" s="54">
         <v>0</v>
       </c>
-      <c r="AG3" s="55" t="s">
+      <c r="AG3" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH3" s="61">
+      <c r="AH3" s="59">
         <v>0</v>
       </c>
-      <c r="AI3" s="61">
+      <c r="AI3" s="59">
         <v>0</v>
       </c>
-      <c r="AJ3" s="61">
+      <c r="AJ3" s="59">
         <v>0.65</v>
       </c>
-      <c r="AK3" s="61">
+      <c r="AK3" s="59">
         <v>600</v>
       </c>
-      <c r="AL3" s="62" t="s">
+      <c r="AL3" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="AM3" s="62" t="s">
+      <c r="AM3" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="AN3" s="63">
+      <c r="AN3" s="61">
         <v>500</v>
       </c>
-      <c r="AO3" s="63">
+      <c r="AO3" s="61">
         <v>10</v>
       </c>
-      <c r="AP3" s="65" t="s">
+      <c r="AP3" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ3" s="65" t="s">
+      <c r="AQ3" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR3" s="65" t="s">
+      <c r="AR3" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS3" s="65" t="s">
+      <c r="AS3" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT3" s="65">
+      <c r="AT3" s="63">
         <v>900</v>
       </c>
-      <c r="AU3" s="65">
+      <c r="AU3" s="63">
         <v>600</v>
       </c>
-      <c r="AV3" s="65" t="s">
+      <c r="AV3" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW3" s="65">
+      <c r="AW3" s="63">
         <v>256</v>
       </c>
       <c r="AX3" s="51">
@@ -2649,7 +2618,7 @@
       <c r="BB3" s="51">
         <v>1</v>
       </c>
-      <c r="BC3" s="67" t="s">
+      <c r="BC3" s="64" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2663,104 +2632,112 @@
       <c r="C4" s="51">
         <v>1</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="41" t="s">
         <v>127</v>
       </c>
       <c r="F4" s="48">
         <v>800</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="53" t="s">
+      <c r="G4" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="H4" s="48" t="s">
         <v>128</v>
       </c>
+      <c r="I4" s="41" t="s">
+        <v>129</v>
+      </c>
       <c r="J4" s="51">
         <v>1</v>
       </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="57">
+      <c r="K4" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="54"/>
+      <c r="U4" s="54"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="54"/>
+      <c r="Y4" s="54"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="56">
         <v>20</v>
       </c>
-      <c r="AB4" s="57">
+      <c r="AB4" s="56">
         <v>20</v>
       </c>
-      <c r="AC4" s="55">
+      <c r="AC4" s="54">
         <v>500</v>
       </c>
-      <c r="AD4" s="55">
+      <c r="AD4" s="54">
         <v>0</v>
       </c>
-      <c r="AE4" s="55">
+      <c r="AE4" s="54">
         <v>50</v>
       </c>
-      <c r="AF4" s="55">
+      <c r="AF4" s="54">
         <v>0</v>
       </c>
-      <c r="AG4" s="55" t="s">
+      <c r="AG4" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH4" s="61">
+      <c r="AH4" s="59">
         <v>50</v>
       </c>
-      <c r="AI4" s="61">
+      <c r="AI4" s="59">
         <v>50</v>
       </c>
-      <c r="AJ4" s="61">
+      <c r="AJ4" s="59">
         <v>0.65</v>
       </c>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM4" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN4" s="63">
+      <c r="AK4" s="59">
+        <v>600</v>
+      </c>
+      <c r="AL4" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM4" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN4" s="61">
         <v>500</v>
       </c>
-      <c r="AO4" s="63">
+      <c r="AO4" s="61">
         <v>10</v>
       </c>
-      <c r="AP4" s="65" t="s">
+      <c r="AP4" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ4" s="65" t="s">
+      <c r="AQ4" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="65" t="s">
+      <c r="AR4" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS4" s="65" t="s">
+      <c r="AS4" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT4" s="65">
+      <c r="AT4" s="63">
         <v>900</v>
       </c>
-      <c r="AU4" s="65">
+      <c r="AU4" s="63">
         <v>600</v>
       </c>
-      <c r="AV4" s="65" t="s">
+      <c r="AV4" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW4" s="65">
+      <c r="AW4" s="63">
         <v>256</v>
       </c>
       <c r="AX4" s="51">
@@ -2782,7 +2759,7 @@
     </row>
     <row r="5" s="3" customFormat="1" spans="1:55">
       <c r="A5" s="51" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" s="51" t="s">
         <v>107</v>
@@ -2790,104 +2767,104 @@
       <c r="C5" s="51">
         <v>1</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>127</v>
+      <c r="D5" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F5" s="48">
         <v>800</v>
       </c>
       <c r="G5" s="48"/>
       <c r="H5" s="48"/>
-      <c r="I5" s="53" t="s">
-        <v>128</v>
+      <c r="I5" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J5" s="51">
         <v>1</v>
       </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="57">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="56">
         <v>30</v>
       </c>
-      <c r="AB5" s="57">
+      <c r="AB5" s="56">
         <v>20</v>
       </c>
-      <c r="AC5" s="55">
+      <c r="AC5" s="54">
         <v>450</v>
       </c>
-      <c r="AD5" s="55">
+      <c r="AD5" s="54">
         <v>0</v>
       </c>
-      <c r="AE5" s="55">
+      <c r="AE5" s="54">
         <v>0</v>
       </c>
-      <c r="AF5" s="55">
+      <c r="AF5" s="54">
         <v>0</v>
       </c>
-      <c r="AG5" s="55" t="s">
+      <c r="AG5" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH5" s="61">
+      <c r="AH5" s="59">
         <v>55</v>
       </c>
-      <c r="AI5" s="61">
+      <c r="AI5" s="59">
         <v>55</v>
       </c>
-      <c r="AJ5" s="61">
+      <c r="AJ5" s="59">
         <v>0.55</v>
       </c>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM5" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN5" s="63">
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM5" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN5" s="61">
         <v>500</v>
       </c>
-      <c r="AO5" s="63">
+      <c r="AO5" s="61">
         <v>10</v>
       </c>
-      <c r="AP5" s="65" t="s">
+      <c r="AP5" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ5" s="65" t="s">
+      <c r="AQ5" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR5" s="65" t="s">
+      <c r="AR5" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS5" s="65" t="s">
+      <c r="AS5" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT5" s="65">
+      <c r="AT5" s="63">
         <v>900</v>
       </c>
-      <c r="AU5" s="65">
+      <c r="AU5" s="63">
         <v>600</v>
       </c>
-      <c r="AV5" s="65" t="s">
+      <c r="AV5" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW5" s="65">
+      <c r="AW5" s="63">
         <v>256</v>
       </c>
       <c r="AX5" s="51">
@@ -2909,7 +2886,7 @@
     </row>
     <row r="6" s="3" customFormat="1" spans="1:55">
       <c r="A6" s="51" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>107</v>
@@ -2917,104 +2894,104 @@
       <c r="C6" s="51">
         <v>1</v>
       </c>
-      <c r="D6" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>127</v>
+      <c r="D6" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F6" s="48">
         <v>800</v>
       </c>
       <c r="G6" s="48"/>
       <c r="H6" s="48"/>
-      <c r="I6" s="53" t="s">
-        <v>128</v>
+      <c r="I6" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J6" s="51">
         <v>1</v>
       </c>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
-      <c r="Z6" s="55"/>
-      <c r="AA6" s="57">
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="56">
         <v>25</v>
       </c>
-      <c r="AB6" s="57">
+      <c r="AB6" s="56">
         <v>20</v>
       </c>
-      <c r="AC6" s="55">
+      <c r="AC6" s="54">
         <v>600</v>
       </c>
-      <c r="AD6" s="55">
+      <c r="AD6" s="54">
         <v>0</v>
       </c>
-      <c r="AE6" s="55">
+      <c r="AE6" s="54">
         <v>35</v>
       </c>
-      <c r="AF6" s="55">
+      <c r="AF6" s="54">
         <v>0</v>
       </c>
-      <c r="AG6" s="55" t="s">
+      <c r="AG6" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH6" s="61">
+      <c r="AH6" s="59">
         <v>65</v>
       </c>
-      <c r="AI6" s="61">
+      <c r="AI6" s="59">
         <v>65</v>
       </c>
-      <c r="AJ6" s="61">
+      <c r="AJ6" s="59">
         <v>0.65</v>
       </c>
-      <c r="AK6" s="61"/>
-      <c r="AL6" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM6" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN6" s="63">
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM6" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN6" s="61">
         <v>500</v>
       </c>
-      <c r="AO6" s="63">
+      <c r="AO6" s="61">
         <v>10</v>
       </c>
-      <c r="AP6" s="65" t="s">
+      <c r="AP6" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ6" s="65" t="s">
+      <c r="AQ6" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR6" s="65" t="s">
+      <c r="AR6" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS6" s="65" t="s">
+      <c r="AS6" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT6" s="65">
+      <c r="AT6" s="63">
         <v>900</v>
       </c>
-      <c r="AU6" s="65">
+      <c r="AU6" s="63">
         <v>600</v>
       </c>
-      <c r="AV6" s="65" t="s">
+      <c r="AV6" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW6" s="65">
+      <c r="AW6" s="63">
         <v>256</v>
       </c>
       <c r="AX6" s="51">
@@ -3036,7 +3013,7 @@
     </row>
     <row r="7" s="3" customFormat="1" spans="1:55">
       <c r="A7" s="51" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>107</v>
@@ -3044,104 +3021,104 @@
       <c r="C7" s="51">
         <v>1</v>
       </c>
-      <c r="D7" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>127</v>
+      <c r="D7" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F7" s="48">
         <v>800</v>
       </c>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
-      <c r="I7" s="53" t="s">
-        <v>128</v>
+      <c r="I7" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J7" s="51">
         <v>1</v>
       </c>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="55"/>
-      <c r="Z7" s="55"/>
-      <c r="AA7" s="57">
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="54"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="56">
         <v>30</v>
       </c>
-      <c r="AB7" s="57">
+      <c r="AB7" s="56">
         <v>20</v>
       </c>
-      <c r="AC7" s="55">
+      <c r="AC7" s="54">
         <v>700</v>
       </c>
-      <c r="AD7" s="55">
+      <c r="AD7" s="54">
         <v>0</v>
       </c>
-      <c r="AE7" s="55">
+      <c r="AE7" s="54">
         <v>150</v>
       </c>
-      <c r="AF7" s="55">
+      <c r="AF7" s="54">
         <v>100</v>
       </c>
-      <c r="AG7" s="55" t="s">
+      <c r="AG7" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH7" s="61">
+      <c r="AH7" s="59">
         <v>65</v>
       </c>
-      <c r="AI7" s="61">
+      <c r="AI7" s="59">
         <v>65</v>
       </c>
-      <c r="AJ7" s="61">
+      <c r="AJ7" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK7" s="61"/>
-      <c r="AL7" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM7" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN7" s="63">
+      <c r="AK7" s="59"/>
+      <c r="AL7" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM7" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN7" s="61">
         <v>500</v>
       </c>
-      <c r="AO7" s="63">
+      <c r="AO7" s="61">
         <v>10</v>
       </c>
-      <c r="AP7" s="65" t="s">
+      <c r="AP7" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ7" s="65" t="s">
+      <c r="AQ7" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR7" s="65" t="s">
+      <c r="AR7" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS7" s="65" t="s">
+      <c r="AS7" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT7" s="65">
+      <c r="AT7" s="63">
         <v>900</v>
       </c>
-      <c r="AU7" s="65">
+      <c r="AU7" s="63">
         <v>600</v>
       </c>
-      <c r="AV7" s="65" t="s">
+      <c r="AV7" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW7" s="65">
+      <c r="AW7" s="63">
         <v>256</v>
       </c>
       <c r="AX7" s="51">
@@ -3163,7 +3140,7 @@
     </row>
     <row r="8" s="3" customFormat="1" spans="1:55">
       <c r="A8" s="51" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>107</v>
@@ -3171,104 +3148,104 @@
       <c r="C8" s="51">
         <v>1</v>
       </c>
-      <c r="D8" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>127</v>
+      <c r="D8" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F8" s="48">
         <v>800</v>
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="48"/>
-      <c r="I8" s="53" t="s">
-        <v>128</v>
+      <c r="I8" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J8" s="51">
         <v>1</v>
       </c>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="55"/>
-      <c r="Z8" s="55"/>
-      <c r="AA8" s="57">
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="56">
         <v>20</v>
       </c>
-      <c r="AB8" s="57">
+      <c r="AB8" s="56">
         <v>20</v>
       </c>
-      <c r="AC8" s="55">
+      <c r="AC8" s="54">
         <v>700</v>
       </c>
-      <c r="AD8" s="55">
+      <c r="AD8" s="54">
         <v>0</v>
       </c>
-      <c r="AE8" s="55">
+      <c r="AE8" s="54">
         <v>100</v>
       </c>
-      <c r="AF8" s="55">
+      <c r="AF8" s="54">
         <v>0</v>
       </c>
-      <c r="AG8" s="55" t="s">
+      <c r="AG8" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH8" s="61">
+      <c r="AH8" s="59">
         <v>60</v>
       </c>
-      <c r="AI8" s="61">
+      <c r="AI8" s="59">
         <v>60</v>
       </c>
-      <c r="AJ8" s="61">
+      <c r="AJ8" s="59">
         <v>0.65</v>
       </c>
-      <c r="AK8" s="61"/>
-      <c r="AL8" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM8" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN8" s="63">
+      <c r="AK8" s="59"/>
+      <c r="AL8" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM8" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN8" s="61">
         <v>500</v>
       </c>
-      <c r="AO8" s="63">
+      <c r="AO8" s="61">
         <v>10</v>
       </c>
-      <c r="AP8" s="65" t="s">
+      <c r="AP8" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ8" s="65" t="s">
+      <c r="AQ8" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR8" s="65" t="s">
+      <c r="AR8" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS8" s="65" t="s">
+      <c r="AS8" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT8" s="65">
+      <c r="AT8" s="63">
         <v>900</v>
       </c>
-      <c r="AU8" s="65">
+      <c r="AU8" s="63">
         <v>600</v>
       </c>
-      <c r="AV8" s="65" t="s">
+      <c r="AV8" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW8" s="65">
+      <c r="AW8" s="63">
         <v>256</v>
       </c>
       <c r="AX8" s="51">
@@ -3290,7 +3267,7 @@
     </row>
     <row r="9" s="3" customFormat="1" spans="1:55">
       <c r="A9" s="51" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B9" s="51" t="s">
         <v>107</v>
@@ -3298,104 +3275,104 @@
       <c r="C9" s="51">
         <v>1</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>127</v>
+      <c r="D9" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F9" s="48">
         <v>800</v>
       </c>
       <c r="G9" s="48"/>
       <c r="H9" s="48"/>
-      <c r="I9" s="53" t="s">
-        <v>128</v>
+      <c r="I9" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J9" s="51">
         <v>1</v>
       </c>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="57">
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="56">
         <v>20</v>
       </c>
-      <c r="AB9" s="57">
+      <c r="AB9" s="56">
         <v>20</v>
       </c>
-      <c r="AC9" s="55">
+      <c r="AC9" s="54">
         <v>550</v>
       </c>
-      <c r="AD9" s="55">
+      <c r="AD9" s="54">
         <v>0</v>
       </c>
-      <c r="AE9" s="55">
+      <c r="AE9" s="54">
         <v>0</v>
       </c>
-      <c r="AF9" s="55">
+      <c r="AF9" s="54">
         <v>0</v>
       </c>
-      <c r="AG9" s="55" t="s">
+      <c r="AG9" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH9" s="61">
+      <c r="AH9" s="59">
         <v>75</v>
       </c>
-      <c r="AI9" s="61">
+      <c r="AI9" s="59">
         <v>75</v>
       </c>
-      <c r="AJ9" s="61">
+      <c r="AJ9" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK9" s="61"/>
-      <c r="AL9" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM9" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN9" s="63">
+      <c r="AK9" s="59"/>
+      <c r="AL9" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM9" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN9" s="61">
         <v>500</v>
       </c>
-      <c r="AO9" s="63">
+      <c r="AO9" s="61">
         <v>10</v>
       </c>
-      <c r="AP9" s="65" t="s">
+      <c r="AP9" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ9" s="65" t="s">
+      <c r="AQ9" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR9" s="65" t="s">
+      <c r="AR9" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS9" s="65" t="s">
+      <c r="AS9" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT9" s="65">
+      <c r="AT9" s="63">
         <v>900</v>
       </c>
-      <c r="AU9" s="65">
+      <c r="AU9" s="63">
         <v>600</v>
       </c>
-      <c r="AV9" s="65" t="s">
+      <c r="AV9" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW9" s="65">
+      <c r="AW9" s="63">
         <v>256</v>
       </c>
       <c r="AX9" s="51">
@@ -3417,7 +3394,7 @@
     </row>
     <row r="10" s="3" customFormat="1" spans="1:55">
       <c r="A10" s="51" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>107</v>
@@ -3425,104 +3402,104 @@
       <c r="C10" s="51">
         <v>1</v>
       </c>
-      <c r="D10" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="53" t="s">
-        <v>127</v>
+      <c r="D10" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F10" s="48">
         <v>800</v>
       </c>
       <c r="G10" s="48"/>
       <c r="H10" s="48"/>
-      <c r="I10" s="53" t="s">
-        <v>128</v>
+      <c r="I10" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J10" s="51">
         <v>1</v>
       </c>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="55"/>
-      <c r="Y10" s="55"/>
-      <c r="Z10" s="55"/>
-      <c r="AA10" s="57">
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="56">
         <v>20</v>
       </c>
-      <c r="AB10" s="57">
+      <c r="AB10" s="56">
         <v>20</v>
       </c>
-      <c r="AC10" s="55">
+      <c r="AC10" s="54">
         <v>750</v>
       </c>
-      <c r="AD10" s="55">
+      <c r="AD10" s="54">
         <v>0</v>
       </c>
-      <c r="AE10" s="55">
+      <c r="AE10" s="54">
         <v>150</v>
       </c>
-      <c r="AF10" s="55">
+      <c r="AF10" s="54">
         <v>0</v>
       </c>
-      <c r="AG10" s="55" t="s">
+      <c r="AG10" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH10" s="61">
+      <c r="AH10" s="59">
         <v>75</v>
       </c>
-      <c r="AI10" s="61">
+      <c r="AI10" s="59">
         <v>75</v>
       </c>
-      <c r="AJ10" s="61">
+      <c r="AJ10" s="59">
         <v>0.95</v>
       </c>
-      <c r="AK10" s="61"/>
-      <c r="AL10" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM10" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN10" s="63">
+      <c r="AK10" s="59"/>
+      <c r="AL10" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM10" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN10" s="61">
         <v>500</v>
       </c>
-      <c r="AO10" s="63">
+      <c r="AO10" s="61">
         <v>10</v>
       </c>
-      <c r="AP10" s="65" t="s">
+      <c r="AP10" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ10" s="65" t="s">
+      <c r="AQ10" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR10" s="65" t="s">
+      <c r="AR10" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS10" s="65" t="s">
+      <c r="AS10" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT10" s="65">
+      <c r="AT10" s="63">
         <v>900</v>
       </c>
-      <c r="AU10" s="65">
+      <c r="AU10" s="63">
         <v>600</v>
       </c>
-      <c r="AV10" s="65" t="s">
+      <c r="AV10" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW10" s="65">
+      <c r="AW10" s="63">
         <v>256</v>
       </c>
       <c r="AX10" s="51">
@@ -3544,7 +3521,7 @@
     </row>
     <row r="11" s="3" customFormat="1" spans="1:55">
       <c r="A11" s="51" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>107</v>
@@ -3552,104 +3529,104 @@
       <c r="C11" s="51">
         <v>1</v>
       </c>
-      <c r="D11" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="53" t="s">
-        <v>127</v>
+      <c r="D11" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F11" s="48">
         <v>800</v>
       </c>
       <c r="G11" s="48"/>
       <c r="H11" s="48"/>
-      <c r="I11" s="53" t="s">
-        <v>128</v>
+      <c r="I11" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J11" s="51">
         <v>1</v>
       </c>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="55"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="57">
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="56">
         <v>25</v>
       </c>
-      <c r="AB11" s="57">
+      <c r="AB11" s="56">
         <v>20</v>
       </c>
-      <c r="AC11" s="55">
+      <c r="AC11" s="54">
         <v>550</v>
       </c>
-      <c r="AD11" s="55">
+      <c r="AD11" s="54">
         <v>0</v>
       </c>
-      <c r="AE11" s="55">
+      <c r="AE11" s="54">
         <v>0</v>
       </c>
-      <c r="AF11" s="55">
+      <c r="AF11" s="54">
         <v>0</v>
       </c>
-      <c r="AG11" s="55" t="s">
+      <c r="AG11" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH11" s="61">
+      <c r="AH11" s="59">
         <v>40</v>
       </c>
-      <c r="AI11" s="61">
+      <c r="AI11" s="59">
         <v>40</v>
       </c>
-      <c r="AJ11" s="61">
+      <c r="AJ11" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK11" s="61"/>
-      <c r="AL11" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM11" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN11" s="63">
+      <c r="AK11" s="59"/>
+      <c r="AL11" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM11" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN11" s="61">
         <v>500</v>
       </c>
-      <c r="AO11" s="63">
+      <c r="AO11" s="61">
         <v>10</v>
       </c>
-      <c r="AP11" s="65" t="s">
+      <c r="AP11" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ11" s="65" t="s">
+      <c r="AQ11" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR11" s="65" t="s">
+      <c r="AR11" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS11" s="65" t="s">
+      <c r="AS11" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT11" s="65">
+      <c r="AT11" s="63">
         <v>900</v>
       </c>
-      <c r="AU11" s="65">
+      <c r="AU11" s="63">
         <v>600</v>
       </c>
-      <c r="AV11" s="65" t="s">
+      <c r="AV11" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW11" s="65">
+      <c r="AW11" s="63">
         <v>256</v>
       </c>
       <c r="AX11" s="51">
@@ -3671,7 +3648,7 @@
     </row>
     <row r="12" s="3" customFormat="1" spans="1:55">
       <c r="A12" s="51" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>107</v>
@@ -3679,104 +3656,104 @@
       <c r="C12" s="51">
         <v>1</v>
       </c>
-      <c r="D12" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>127</v>
+      <c r="D12" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F12" s="48">
         <v>800</v>
       </c>
       <c r="G12" s="48"/>
       <c r="H12" s="48"/>
-      <c r="I12" s="53" t="s">
-        <v>128</v>
+      <c r="I12" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J12" s="51">
         <v>1</v>
       </c>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
-      <c r="Z12" s="55"/>
-      <c r="AA12" s="57">
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="56">
         <v>20</v>
       </c>
-      <c r="AB12" s="57">
+      <c r="AB12" s="56">
         <v>20</v>
       </c>
-      <c r="AC12" s="55">
+      <c r="AC12" s="54">
         <v>500</v>
       </c>
-      <c r="AD12" s="55">
+      <c r="AD12" s="54">
         <v>0</v>
       </c>
-      <c r="AE12" s="55">
+      <c r="AE12" s="54">
         <v>50</v>
       </c>
-      <c r="AF12" s="55">
+      <c r="AF12" s="54">
         <v>0</v>
       </c>
-      <c r="AG12" s="55" t="s">
+      <c r="AG12" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH12" s="61">
+      <c r="AH12" s="59">
         <v>40</v>
       </c>
-      <c r="AI12" s="61">
+      <c r="AI12" s="59">
         <v>40</v>
       </c>
-      <c r="AJ12" s="61">
+      <c r="AJ12" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK12" s="61"/>
-      <c r="AL12" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM12" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN12" s="63">
+      <c r="AK12" s="59"/>
+      <c r="AL12" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM12" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN12" s="61">
         <v>500</v>
       </c>
-      <c r="AO12" s="63">
+      <c r="AO12" s="61">
         <v>10</v>
       </c>
-      <c r="AP12" s="65" t="s">
+      <c r="AP12" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ12" s="65" t="s">
+      <c r="AQ12" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR12" s="65" t="s">
+      <c r="AR12" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS12" s="65" t="s">
+      <c r="AS12" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT12" s="65">
+      <c r="AT12" s="63">
         <v>900</v>
       </c>
-      <c r="AU12" s="65">
+      <c r="AU12" s="63">
         <v>600</v>
       </c>
-      <c r="AV12" s="65" t="s">
+      <c r="AV12" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW12" s="65">
+      <c r="AW12" s="63">
         <v>256</v>
       </c>
       <c r="AX12" s="51">
@@ -3798,7 +3775,7 @@
     </row>
     <row r="13" s="3" customFormat="1" spans="1:55">
       <c r="A13" s="51" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B13" s="51" t="s">
         <v>107</v>
@@ -3806,104 +3783,104 @@
       <c r="C13" s="51">
         <v>1</v>
       </c>
-      <c r="D13" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="53" t="s">
-        <v>127</v>
+      <c r="D13" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F13" s="48">
         <v>800</v>
       </c>
       <c r="G13" s="48"/>
       <c r="H13" s="48"/>
-      <c r="I13" s="53" t="s">
-        <v>128</v>
+      <c r="I13" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J13" s="51">
         <v>1</v>
       </c>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="55"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="55"/>
-      <c r="Z13" s="55"/>
-      <c r="AA13" s="57">
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="56">
         <v>25</v>
       </c>
-      <c r="AB13" s="57">
+      <c r="AB13" s="56">
         <v>20</v>
       </c>
-      <c r="AC13" s="55">
+      <c r="AC13" s="54">
         <v>500</v>
       </c>
-      <c r="AD13" s="55">
+      <c r="AD13" s="54">
         <v>0</v>
       </c>
-      <c r="AE13" s="55">
+      <c r="AE13" s="54">
         <v>75</v>
       </c>
-      <c r="AF13" s="55">
+      <c r="AF13" s="54">
         <v>0</v>
       </c>
-      <c r="AG13" s="55" t="s">
+      <c r="AG13" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH13" s="61">
+      <c r="AH13" s="59">
         <v>60</v>
       </c>
-      <c r="AI13" s="61">
+      <c r="AI13" s="59">
         <v>60</v>
       </c>
-      <c r="AJ13" s="61">
+      <c r="AJ13" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK13" s="61"/>
-      <c r="AL13" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM13" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN13" s="63">
+      <c r="AK13" s="59"/>
+      <c r="AL13" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM13" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN13" s="61">
         <v>500</v>
       </c>
-      <c r="AO13" s="63">
+      <c r="AO13" s="61">
         <v>10</v>
       </c>
-      <c r="AP13" s="65" t="s">
+      <c r="AP13" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ13" s="65" t="s">
+      <c r="AQ13" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR13" s="65" t="s">
+      <c r="AR13" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS13" s="65" t="s">
+      <c r="AS13" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT13" s="65">
+      <c r="AT13" s="63">
         <v>900</v>
       </c>
-      <c r="AU13" s="65">
+      <c r="AU13" s="63">
         <v>600</v>
       </c>
-      <c r="AV13" s="65" t="s">
+      <c r="AV13" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW13" s="65">
+      <c r="AW13" s="63">
         <v>256</v>
       </c>
       <c r="AX13" s="51">
@@ -3925,7 +3902,7 @@
     </row>
     <row r="14" s="3" customFormat="1" spans="1:55">
       <c r="A14" s="51" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>107</v>
@@ -3933,104 +3910,104 @@
       <c r="C14" s="51">
         <v>1</v>
       </c>
-      <c r="D14" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" s="53" t="s">
-        <v>127</v>
+      <c r="D14" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F14" s="48">
         <v>800</v>
       </c>
       <c r="G14" s="48"/>
       <c r="H14" s="48"/>
-      <c r="I14" s="53" t="s">
-        <v>128</v>
+      <c r="I14" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J14" s="51">
         <v>1</v>
       </c>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="55"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="55"/>
-      <c r="Y14" s="55"/>
-      <c r="Z14" s="55"/>
-      <c r="AA14" s="57">
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="54"/>
+      <c r="V14" s="54"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="56">
         <v>20</v>
       </c>
-      <c r="AB14" s="57">
+      <c r="AB14" s="56">
         <v>20</v>
       </c>
-      <c r="AC14" s="55">
+      <c r="AC14" s="54">
         <v>550</v>
       </c>
-      <c r="AD14" s="55">
+      <c r="AD14" s="54">
         <v>0</v>
       </c>
-      <c r="AE14" s="55">
+      <c r="AE14" s="54">
         <v>125</v>
       </c>
-      <c r="AF14" s="55">
+      <c r="AF14" s="54">
         <v>0</v>
       </c>
-      <c r="AG14" s="55" t="s">
+      <c r="AG14" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH14" s="61">
+      <c r="AH14" s="59">
         <v>65</v>
       </c>
-      <c r="AI14" s="61">
+      <c r="AI14" s="59">
         <v>65</v>
       </c>
-      <c r="AJ14" s="61">
+      <c r="AJ14" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK14" s="61"/>
-      <c r="AL14" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM14" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN14" s="63">
+      <c r="AK14" s="59"/>
+      <c r="AL14" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM14" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN14" s="61">
         <v>500</v>
       </c>
-      <c r="AO14" s="63">
+      <c r="AO14" s="61">
         <v>10</v>
       </c>
-      <c r="AP14" s="65" t="s">
+      <c r="AP14" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ14" s="65" t="s">
+      <c r="AQ14" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR14" s="65" t="s">
+      <c r="AR14" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS14" s="65" t="s">
+      <c r="AS14" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT14" s="65">
+      <c r="AT14" s="63">
         <v>900</v>
       </c>
-      <c r="AU14" s="65">
+      <c r="AU14" s="63">
         <v>600</v>
       </c>
-      <c r="AV14" s="65" t="s">
+      <c r="AV14" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW14" s="65">
+      <c r="AW14" s="63">
         <v>256</v>
       </c>
       <c r="AX14" s="51">
@@ -4052,7 +4029,7 @@
     </row>
     <row r="15" s="3" customFormat="1" spans="1:55">
       <c r="A15" s="51" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B15" s="51" t="s">
         <v>107</v>
@@ -4060,104 +4037,104 @@
       <c r="C15" s="51">
         <v>1</v>
       </c>
-      <c r="D15" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="53" t="s">
-        <v>127</v>
+      <c r="D15" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F15" s="48">
         <v>800</v>
       </c>
       <c r="G15" s="48"/>
       <c r="H15" s="48"/>
-      <c r="I15" s="53" t="s">
-        <v>128</v>
+      <c r="I15" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J15" s="51">
         <v>1</v>
       </c>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="55"/>
-      <c r="U15" s="55"/>
-      <c r="V15" s="55"/>
-      <c r="W15" s="55"/>
-      <c r="X15" s="55"/>
-      <c r="Y15" s="55"/>
-      <c r="Z15" s="55"/>
-      <c r="AA15" s="57">
+      <c r="K15" s="54"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="56">
         <v>20</v>
       </c>
-      <c r="AB15" s="57">
+      <c r="AB15" s="56">
         <v>20</v>
       </c>
-      <c r="AC15" s="55">
+      <c r="AC15" s="54">
         <v>600</v>
       </c>
-      <c r="AD15" s="55">
+      <c r="AD15" s="54">
         <v>0</v>
       </c>
-      <c r="AE15" s="55">
+      <c r="AE15" s="54">
         <v>150</v>
       </c>
-      <c r="AF15" s="55">
+      <c r="AF15" s="54">
         <v>50</v>
       </c>
-      <c r="AG15" s="55" t="s">
+      <c r="AG15" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH15" s="61">
+      <c r="AH15" s="59">
         <v>60</v>
       </c>
-      <c r="AI15" s="61">
+      <c r="AI15" s="59">
         <v>60</v>
       </c>
-      <c r="AJ15" s="61">
+      <c r="AJ15" s="59">
         <v>0.7</v>
       </c>
-      <c r="AK15" s="61"/>
-      <c r="AL15" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM15" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN15" s="63">
+      <c r="AK15" s="59"/>
+      <c r="AL15" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM15" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN15" s="61">
         <v>500</v>
       </c>
-      <c r="AO15" s="63">
+      <c r="AO15" s="61">
         <v>10</v>
       </c>
-      <c r="AP15" s="65" t="s">
+      <c r="AP15" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ15" s="65" t="s">
+      <c r="AQ15" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR15" s="65" t="s">
+      <c r="AR15" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS15" s="65" t="s">
+      <c r="AS15" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT15" s="65">
+      <c r="AT15" s="63">
         <v>900</v>
       </c>
-      <c r="AU15" s="65">
+      <c r="AU15" s="63">
         <v>600</v>
       </c>
-      <c r="AV15" s="65" t="s">
+      <c r="AV15" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW15" s="65">
+      <c r="AW15" s="63">
         <v>256</v>
       </c>
       <c r="AX15" s="51">
@@ -4179,7 +4156,7 @@
     </row>
     <row r="16" s="3" customFormat="1" spans="1:55">
       <c r="A16" s="51" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>107</v>
@@ -4187,104 +4164,104 @@
       <c r="C16" s="51">
         <v>1</v>
       </c>
-      <c r="D16" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>127</v>
+      <c r="D16" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F16" s="48">
         <v>800</v>
       </c>
       <c r="G16" s="48"/>
       <c r="H16" s="48"/>
-      <c r="I16" s="53" t="s">
-        <v>128</v>
+      <c r="I16" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J16" s="51">
         <v>1</v>
       </c>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="55"/>
-      <c r="U16" s="55"/>
-      <c r="V16" s="55"/>
-      <c r="W16" s="55"/>
-      <c r="X16" s="55"/>
-      <c r="Y16" s="55"/>
-      <c r="Z16" s="55"/>
-      <c r="AA16" s="57">
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="54"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="56">
         <v>20</v>
       </c>
-      <c r="AB16" s="57">
+      <c r="AB16" s="56">
         <v>20</v>
       </c>
-      <c r="AC16" s="55">
+      <c r="AC16" s="54">
         <v>700</v>
       </c>
-      <c r="AD16" s="55">
+      <c r="AD16" s="54">
         <v>0</v>
       </c>
-      <c r="AE16" s="55">
+      <c r="AE16" s="54">
         <v>125</v>
       </c>
-      <c r="AF16" s="55">
+      <c r="AF16" s="54">
         <v>50</v>
       </c>
-      <c r="AG16" s="55" t="s">
+      <c r="AG16" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH16" s="61">
+      <c r="AH16" s="59">
         <v>55</v>
       </c>
-      <c r="AI16" s="61">
+      <c r="AI16" s="59">
         <v>55</v>
       </c>
-      <c r="AJ16" s="61">
+      <c r="AJ16" s="59">
         <v>1.25</v>
       </c>
-      <c r="AK16" s="61"/>
-      <c r="AL16" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM16" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN16" s="63">
+      <c r="AK16" s="59"/>
+      <c r="AL16" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM16" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN16" s="61">
         <v>500</v>
       </c>
-      <c r="AO16" s="63">
+      <c r="AO16" s="61">
         <v>10</v>
       </c>
-      <c r="AP16" s="65" t="s">
+      <c r="AP16" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ16" s="65" t="s">
+      <c r="AQ16" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR16" s="65" t="s">
+      <c r="AR16" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS16" s="65" t="s">
+      <c r="AS16" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT16" s="65">
+      <c r="AT16" s="63">
         <v>900</v>
       </c>
-      <c r="AU16" s="65">
+      <c r="AU16" s="63">
         <v>600</v>
       </c>
-      <c r="AV16" s="65" t="s">
+      <c r="AV16" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW16" s="65">
+      <c r="AW16" s="63">
         <v>256</v>
       </c>
       <c r="AX16" s="51">
@@ -4306,7 +4283,7 @@
     </row>
     <row r="17" s="3" customFormat="1" spans="1:55">
       <c r="A17" s="51" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>107</v>
@@ -4314,104 +4291,104 @@
       <c r="C17" s="51">
         <v>1</v>
       </c>
-      <c r="D17" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>127</v>
+      <c r="D17" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F17" s="48">
         <v>800</v>
       </c>
       <c r="G17" s="48"/>
       <c r="H17" s="48"/>
-      <c r="I17" s="53" t="s">
-        <v>128</v>
+      <c r="I17" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J17" s="51">
         <v>1</v>
       </c>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="55"/>
-      <c r="V17" s="55"/>
-      <c r="W17" s="55"/>
-      <c r="X17" s="55"/>
-      <c r="Y17" s="55"/>
-      <c r="Z17" s="55"/>
-      <c r="AA17" s="57">
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="54"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="56">
         <v>20</v>
       </c>
-      <c r="AB17" s="57">
+      <c r="AB17" s="56">
         <v>20</v>
       </c>
-      <c r="AC17" s="55">
+      <c r="AC17" s="54">
         <v>500</v>
       </c>
-      <c r="AD17" s="55">
+      <c r="AD17" s="54">
         <v>0</v>
       </c>
-      <c r="AE17" s="55">
+      <c r="AE17" s="54">
         <v>100</v>
       </c>
-      <c r="AF17" s="55">
+      <c r="AF17" s="54">
         <v>0</v>
       </c>
-      <c r="AG17" s="55" t="s">
+      <c r="AG17" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH17" s="61">
+      <c r="AH17" s="59">
         <v>45</v>
       </c>
-      <c r="AI17" s="61">
+      <c r="AI17" s="59">
         <v>45</v>
       </c>
-      <c r="AJ17" s="61">
+      <c r="AJ17" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK17" s="61"/>
-      <c r="AL17" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM17" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN17" s="63">
+      <c r="AK17" s="59"/>
+      <c r="AL17" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM17" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN17" s="61">
         <v>500</v>
       </c>
-      <c r="AO17" s="63">
+      <c r="AO17" s="61">
         <v>10</v>
       </c>
-      <c r="AP17" s="65" t="s">
+      <c r="AP17" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ17" s="65" t="s">
+      <c r="AQ17" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR17" s="65" t="s">
+      <c r="AR17" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS17" s="65" t="s">
+      <c r="AS17" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT17" s="65">
+      <c r="AT17" s="63">
         <v>900</v>
       </c>
-      <c r="AU17" s="65">
+      <c r="AU17" s="63">
         <v>600</v>
       </c>
-      <c r="AV17" s="65" t="s">
+      <c r="AV17" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW17" s="65">
+      <c r="AW17" s="63">
         <v>256</v>
       </c>
       <c r="AX17" s="51">
@@ -4433,7 +4410,7 @@
     </row>
     <row r="18" s="3" customFormat="1" spans="1:55">
       <c r="A18" s="51" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B18" s="51" t="s">
         <v>107</v>
@@ -4441,104 +4418,104 @@
       <c r="C18" s="51">
         <v>1</v>
       </c>
-      <c r="D18" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>127</v>
+      <c r="D18" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F18" s="48">
         <v>800</v>
       </c>
       <c r="G18" s="48"/>
       <c r="H18" s="48"/>
-      <c r="I18" s="53" t="s">
-        <v>128</v>
+      <c r="I18" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J18" s="51">
         <v>1</v>
       </c>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="55"/>
-      <c r="V18" s="55"/>
-      <c r="W18" s="55"/>
-      <c r="X18" s="55"/>
-      <c r="Y18" s="55"/>
-      <c r="Z18" s="55"/>
-      <c r="AA18" s="57">
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="54"/>
+      <c r="W18" s="54"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="56">
         <v>30</v>
       </c>
-      <c r="AB18" s="57">
+      <c r="AB18" s="56">
         <v>20</v>
       </c>
-      <c r="AC18" s="55">
+      <c r="AC18" s="54">
         <v>650</v>
       </c>
-      <c r="AD18" s="55">
+      <c r="AD18" s="54">
         <v>0</v>
       </c>
-      <c r="AE18" s="55">
+      <c r="AE18" s="54">
         <v>150</v>
       </c>
-      <c r="AF18" s="55">
+      <c r="AF18" s="54">
         <v>50</v>
       </c>
-      <c r="AG18" s="55" t="s">
+      <c r="AG18" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH18" s="61">
+      <c r="AH18" s="59">
         <v>50</v>
       </c>
-      <c r="AI18" s="61">
+      <c r="AI18" s="59">
         <v>50</v>
       </c>
-      <c r="AJ18" s="61">
+      <c r="AJ18" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK18" s="61"/>
-      <c r="AL18" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM18" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN18" s="63">
+      <c r="AK18" s="59"/>
+      <c r="AL18" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM18" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN18" s="61">
         <v>500</v>
       </c>
-      <c r="AO18" s="63">
+      <c r="AO18" s="61">
         <v>10</v>
       </c>
-      <c r="AP18" s="65" t="s">
+      <c r="AP18" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ18" s="65" t="s">
+      <c r="AQ18" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR18" s="65" t="s">
+      <c r="AR18" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS18" s="65" t="s">
+      <c r="AS18" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT18" s="65">
+      <c r="AT18" s="63">
         <v>900</v>
       </c>
-      <c r="AU18" s="65">
+      <c r="AU18" s="63">
         <v>600</v>
       </c>
-      <c r="AV18" s="65" t="s">
+      <c r="AV18" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW18" s="65">
+      <c r="AW18" s="63">
         <v>256</v>
       </c>
       <c r="AX18" s="51">
@@ -4560,7 +4537,7 @@
     </row>
     <row r="19" s="3" customFormat="1" spans="1:55">
       <c r="A19" s="51" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B19" s="51" t="s">
         <v>107</v>
@@ -4568,104 +4545,104 @@
       <c r="C19" s="51">
         <v>1</v>
       </c>
-      <c r="D19" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>127</v>
+      <c r="D19" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F19" s="48">
         <v>800</v>
       </c>
       <c r="G19" s="48"/>
       <c r="H19" s="48"/>
-      <c r="I19" s="53" t="s">
-        <v>128</v>
+      <c r="I19" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J19" s="51">
         <v>1</v>
       </c>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="55"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="55"/>
-      <c r="V19" s="55"/>
-      <c r="W19" s="55"/>
-      <c r="X19" s="55"/>
-      <c r="Y19" s="55"/>
-      <c r="Z19" s="55"/>
-      <c r="AA19" s="57">
+      <c r="K19" s="54"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+      <c r="V19" s="54"/>
+      <c r="W19" s="54"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="56">
         <v>20</v>
       </c>
-      <c r="AB19" s="57">
+      <c r="AB19" s="56">
         <v>20</v>
       </c>
-      <c r="AC19" s="55">
+      <c r="AC19" s="54">
         <v>550</v>
       </c>
-      <c r="AD19" s="55">
+      <c r="AD19" s="54">
         <v>0</v>
       </c>
-      <c r="AE19" s="55">
+      <c r="AE19" s="54">
         <v>75</v>
       </c>
-      <c r="AF19" s="55">
+      <c r="AF19" s="54">
         <v>0</v>
       </c>
-      <c r="AG19" s="55" t="s">
+      <c r="AG19" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH19" s="61">
+      <c r="AH19" s="59">
         <v>70</v>
       </c>
-      <c r="AI19" s="61">
+      <c r="AI19" s="59">
         <v>70</v>
       </c>
-      <c r="AJ19" s="61">
+      <c r="AJ19" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK19" s="61"/>
-      <c r="AL19" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM19" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN19" s="63">
+      <c r="AK19" s="59"/>
+      <c r="AL19" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM19" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN19" s="61">
         <v>500</v>
       </c>
-      <c r="AO19" s="63">
+      <c r="AO19" s="61">
         <v>10</v>
       </c>
-      <c r="AP19" s="65" t="s">
+      <c r="AP19" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ19" s="65" t="s">
+      <c r="AQ19" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR19" s="65" t="s">
+      <c r="AR19" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS19" s="65" t="s">
+      <c r="AS19" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT19" s="65">
+      <c r="AT19" s="63">
         <v>900</v>
       </c>
-      <c r="AU19" s="65">
+      <c r="AU19" s="63">
         <v>600</v>
       </c>
-      <c r="AV19" s="65" t="s">
+      <c r="AV19" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW19" s="65">
+      <c r="AW19" s="63">
         <v>256</v>
       </c>
       <c r="AX19" s="51">
@@ -4687,7 +4664,7 @@
     </row>
     <row r="20" s="3" customFormat="1" spans="1:55">
       <c r="A20" s="51" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>107</v>
@@ -4695,104 +4672,104 @@
       <c r="C20" s="51">
         <v>1</v>
       </c>
-      <c r="D20" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>127</v>
+      <c r="D20" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F20" s="48">
         <v>800</v>
       </c>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
-      <c r="I20" s="53" t="s">
-        <v>128</v>
+      <c r="I20" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J20" s="51">
         <v>1</v>
       </c>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="55"/>
-      <c r="U20" s="55"/>
-      <c r="V20" s="55"/>
-      <c r="W20" s="55"/>
-      <c r="X20" s="55"/>
-      <c r="Y20" s="55"/>
-      <c r="Z20" s="55"/>
-      <c r="AA20" s="57">
+      <c r="K20" s="54"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+      <c r="V20" s="54"/>
+      <c r="W20" s="54"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="54"/>
+      <c r="Z20" s="54"/>
+      <c r="AA20" s="56">
         <v>25</v>
       </c>
-      <c r="AB20" s="57">
+      <c r="AB20" s="56">
         <v>20</v>
       </c>
-      <c r="AC20" s="55">
+      <c r="AC20" s="54">
         <v>700</v>
       </c>
-      <c r="AD20" s="55">
+      <c r="AD20" s="54">
         <v>0</v>
       </c>
-      <c r="AE20" s="55">
+      <c r="AE20" s="54">
         <v>150</v>
       </c>
-      <c r="AF20" s="55">
+      <c r="AF20" s="54">
         <v>50</v>
       </c>
-      <c r="AG20" s="55" t="s">
+      <c r="AG20" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH20" s="61">
+      <c r="AH20" s="59">
         <v>60</v>
       </c>
-      <c r="AI20" s="61">
+      <c r="AI20" s="59">
         <v>60</v>
       </c>
-      <c r="AJ20" s="61">
+      <c r="AJ20" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK20" s="61"/>
-      <c r="AL20" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM20" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN20" s="63">
+      <c r="AK20" s="59"/>
+      <c r="AL20" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM20" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN20" s="61">
         <v>500</v>
       </c>
-      <c r="AO20" s="63">
+      <c r="AO20" s="61">
         <v>10</v>
       </c>
-      <c r="AP20" s="65" t="s">
+      <c r="AP20" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ20" s="65" t="s">
+      <c r="AQ20" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR20" s="65" t="s">
+      <c r="AR20" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS20" s="65" t="s">
+      <c r="AS20" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT20" s="65">
+      <c r="AT20" s="63">
         <v>900</v>
       </c>
-      <c r="AU20" s="65">
+      <c r="AU20" s="63">
         <v>600</v>
       </c>
-      <c r="AV20" s="65" t="s">
+      <c r="AV20" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW20" s="65">
+      <c r="AW20" s="63">
         <v>256</v>
       </c>
       <c r="AX20" s="51">
@@ -4814,7 +4791,7 @@
     </row>
     <row r="21" s="3" customFormat="1" spans="1:55">
       <c r="A21" s="51" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>107</v>
@@ -4822,104 +4799,104 @@
       <c r="C21" s="51">
         <v>1</v>
       </c>
-      <c r="D21" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>127</v>
+      <c r="D21" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F21" s="48">
         <v>800</v>
       </c>
       <c r="G21" s="48"/>
       <c r="H21" s="48"/>
-      <c r="I21" s="53" t="s">
-        <v>128</v>
+      <c r="I21" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J21" s="51">
         <v>1</v>
       </c>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="55"/>
-      <c r="U21" s="55"/>
-      <c r="V21" s="55"/>
-      <c r="W21" s="55"/>
-      <c r="X21" s="55"/>
-      <c r="Y21" s="55"/>
-      <c r="Z21" s="55"/>
-      <c r="AA21" s="57">
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+      <c r="V21" s="54"/>
+      <c r="W21" s="54"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="54"/>
+      <c r="Z21" s="54"/>
+      <c r="AA21" s="56">
         <v>25</v>
       </c>
-      <c r="AB21" s="57">
+      <c r="AB21" s="56">
         <v>20</v>
       </c>
-      <c r="AC21" s="55">
+      <c r="AC21" s="54">
         <v>850</v>
       </c>
-      <c r="AD21" s="55">
+      <c r="AD21" s="54">
         <v>0</v>
       </c>
-      <c r="AE21" s="55">
+      <c r="AE21" s="54">
         <v>100</v>
       </c>
-      <c r="AF21" s="55">
+      <c r="AF21" s="54">
         <v>0</v>
       </c>
-      <c r="AG21" s="55" t="s">
+      <c r="AG21" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH21" s="61">
+      <c r="AH21" s="59">
         <v>65</v>
       </c>
-      <c r="AI21" s="61">
+      <c r="AI21" s="59">
         <v>65</v>
       </c>
-      <c r="AJ21" s="61">
+      <c r="AJ21" s="59">
         <v>0.65</v>
       </c>
-      <c r="AK21" s="61"/>
-      <c r="AL21" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM21" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN21" s="63">
+      <c r="AK21" s="59"/>
+      <c r="AL21" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM21" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN21" s="61">
         <v>500</v>
       </c>
-      <c r="AO21" s="63">
+      <c r="AO21" s="61">
         <v>10</v>
       </c>
-      <c r="AP21" s="65" t="s">
+      <c r="AP21" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ21" s="65" t="s">
+      <c r="AQ21" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR21" s="65" t="s">
+      <c r="AR21" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS21" s="65" t="s">
+      <c r="AS21" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT21" s="65">
+      <c r="AT21" s="63">
         <v>900</v>
       </c>
-      <c r="AU21" s="65">
+      <c r="AU21" s="63">
         <v>600</v>
       </c>
-      <c r="AV21" s="65" t="s">
+      <c r="AV21" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW21" s="65">
+      <c r="AW21" s="63">
         <v>256</v>
       </c>
       <c r="AX21" s="51">
@@ -4941,7 +4918,7 @@
     </row>
     <row r="22" s="3" customFormat="1" spans="1:55">
       <c r="A22" s="51" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>107</v>
@@ -4949,104 +4926,104 @@
       <c r="C22" s="51">
         <v>1</v>
       </c>
-      <c r="D22" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>127</v>
+      <c r="D22" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F22" s="48">
         <v>800</v>
       </c>
       <c r="G22" s="48"/>
       <c r="H22" s="48"/>
-      <c r="I22" s="53" t="s">
-        <v>128</v>
+      <c r="I22" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J22" s="51">
         <v>1</v>
       </c>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="55"/>
-      <c r="V22" s="55"/>
-      <c r="W22" s="55"/>
-      <c r="X22" s="55"/>
-      <c r="Y22" s="55"/>
-      <c r="Z22" s="55"/>
-      <c r="AA22" s="57">
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+      <c r="V22" s="54"/>
+      <c r="W22" s="54"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="54"/>
+      <c r="AA22" s="56">
         <v>40</v>
       </c>
-      <c r="AB22" s="57">
+      <c r="AB22" s="56">
         <v>20</v>
       </c>
-      <c r="AC22" s="55">
+      <c r="AC22" s="54">
         <v>600</v>
       </c>
-      <c r="AD22" s="55">
+      <c r="AD22" s="54">
         <v>0</v>
       </c>
-      <c r="AE22" s="55">
+      <c r="AE22" s="54">
         <v>100</v>
       </c>
-      <c r="AF22" s="55">
+      <c r="AF22" s="54">
         <v>0</v>
       </c>
-      <c r="AG22" s="55" t="s">
+      <c r="AG22" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH22" s="61">
+      <c r="AH22" s="59">
         <v>50</v>
       </c>
-      <c r="AI22" s="61">
+      <c r="AI22" s="59">
         <v>50</v>
       </c>
-      <c r="AJ22" s="61">
+      <c r="AJ22" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK22" s="61"/>
-      <c r="AL22" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM22" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN22" s="63">
+      <c r="AK22" s="59"/>
+      <c r="AL22" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM22" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN22" s="61">
         <v>500</v>
       </c>
-      <c r="AO22" s="63">
+      <c r="AO22" s="61">
         <v>10</v>
       </c>
-      <c r="AP22" s="65" t="s">
+      <c r="AP22" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ22" s="65" t="s">
+      <c r="AQ22" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR22" s="65" t="s">
+      <c r="AR22" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS22" s="65" t="s">
+      <c r="AS22" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT22" s="65">
+      <c r="AT22" s="63">
         <v>900</v>
       </c>
-      <c r="AU22" s="65">
+      <c r="AU22" s="63">
         <v>600</v>
       </c>
-      <c r="AV22" s="65" t="s">
+      <c r="AV22" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW22" s="65">
+      <c r="AW22" s="63">
         <v>256</v>
       </c>
       <c r="AX22" s="51">
@@ -5068,7 +5045,7 @@
     </row>
     <row r="23" s="3" customFormat="1" spans="1:55">
       <c r="A23" s="51" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B23" s="51" t="s">
         <v>107</v>
@@ -5076,104 +5053,104 @@
       <c r="C23" s="51">
         <v>1</v>
       </c>
-      <c r="D23" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>127</v>
+      <c r="D23" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F23" s="48">
         <v>800</v>
       </c>
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
-      <c r="I23" s="53" t="s">
-        <v>128</v>
+      <c r="I23" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J23" s="51">
         <v>1</v>
       </c>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="55"/>
-      <c r="V23" s="55"/>
-      <c r="W23" s="55"/>
-      <c r="X23" s="55"/>
-      <c r="Y23" s="55"/>
-      <c r="Z23" s="55"/>
-      <c r="AA23" s="57">
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="54"/>
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="56">
         <v>25</v>
       </c>
-      <c r="AB23" s="57">
+      <c r="AB23" s="56">
         <v>20</v>
       </c>
-      <c r="AC23" s="55">
+      <c r="AC23" s="54">
         <v>450</v>
       </c>
-      <c r="AD23" s="55">
+      <c r="AD23" s="54">
         <v>0</v>
       </c>
-      <c r="AE23" s="55">
+      <c r="AE23" s="54">
         <v>75</v>
       </c>
-      <c r="AF23" s="55">
+      <c r="AF23" s="54">
         <v>0</v>
       </c>
-      <c r="AG23" s="55" t="s">
+      <c r="AG23" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH23" s="61">
+      <c r="AH23" s="59">
         <v>40</v>
       </c>
-      <c r="AI23" s="61">
+      <c r="AI23" s="59">
         <v>40</v>
       </c>
-      <c r="AJ23" s="61">
-        <v>1</v>
-      </c>
-      <c r="AK23" s="61"/>
-      <c r="AL23" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM23" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN23" s="63">
+      <c r="AJ23" s="59">
+        <v>1</v>
+      </c>
+      <c r="AK23" s="59"/>
+      <c r="AL23" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM23" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN23" s="61">
         <v>500</v>
       </c>
-      <c r="AO23" s="63">
+      <c r="AO23" s="61">
         <v>10</v>
       </c>
-      <c r="AP23" s="65" t="s">
+      <c r="AP23" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ23" s="65" t="s">
+      <c r="AQ23" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR23" s="65" t="s">
+      <c r="AR23" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS23" s="65" t="s">
+      <c r="AS23" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT23" s="65">
+      <c r="AT23" s="63">
         <v>900</v>
       </c>
-      <c r="AU23" s="65">
+      <c r="AU23" s="63">
         <v>600</v>
       </c>
-      <c r="AV23" s="65" t="s">
+      <c r="AV23" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW23" s="65">
+      <c r="AW23" s="63">
         <v>256</v>
       </c>
       <c r="AX23" s="51">
@@ -5195,7 +5172,7 @@
     </row>
     <row r="24" s="3" customFormat="1" spans="1:55">
       <c r="A24" s="51" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B24" s="51" t="s">
         <v>107</v>
@@ -5203,104 +5180,104 @@
       <c r="C24" s="51">
         <v>1</v>
       </c>
-      <c r="D24" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>127</v>
+      <c r="D24" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F24" s="48">
         <v>800</v>
       </c>
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
-      <c r="I24" s="53" t="s">
-        <v>128</v>
+      <c r="I24" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J24" s="51">
         <v>1</v>
       </c>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55"/>
-      <c r="U24" s="55"/>
-      <c r="V24" s="55"/>
-      <c r="W24" s="55"/>
-      <c r="X24" s="55"/>
-      <c r="Y24" s="55"/>
-      <c r="Z24" s="55"/>
-      <c r="AA24" s="57">
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+      <c r="V24" s="54"/>
+      <c r="W24" s="54"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="54"/>
+      <c r="Z24" s="54"/>
+      <c r="AA24" s="56">
         <v>50</v>
       </c>
-      <c r="AB24" s="57">
+      <c r="AB24" s="56">
         <v>50</v>
       </c>
-      <c r="AC24" s="55">
+      <c r="AC24" s="54">
         <v>800</v>
       </c>
-      <c r="AD24" s="55">
+      <c r="AD24" s="54">
         <v>0</v>
       </c>
-      <c r="AE24" s="55">
+      <c r="AE24" s="54">
         <v>90</v>
       </c>
-      <c r="AF24" s="55">
+      <c r="AF24" s="54">
         <v>50</v>
       </c>
-      <c r="AG24" s="55" t="s">
+      <c r="AG24" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH24" s="61">
+      <c r="AH24" s="59">
         <v>55</v>
       </c>
-      <c r="AI24" s="61">
+      <c r="AI24" s="59">
         <v>55</v>
       </c>
-      <c r="AJ24" s="61">
+      <c r="AJ24" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK24" s="61"/>
-      <c r="AL24" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM24" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN24" s="63">
+      <c r="AK24" s="59"/>
+      <c r="AL24" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM24" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN24" s="61">
         <v>500</v>
       </c>
-      <c r="AO24" s="63">
+      <c r="AO24" s="61">
         <v>10</v>
       </c>
-      <c r="AP24" s="65" t="s">
+      <c r="AP24" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ24" s="65" t="s">
+      <c r="AQ24" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR24" s="65" t="s">
+      <c r="AR24" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS24" s="65" t="s">
+      <c r="AS24" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT24" s="65">
+      <c r="AT24" s="63">
         <v>900</v>
       </c>
-      <c r="AU24" s="65">
+      <c r="AU24" s="63">
         <v>600</v>
       </c>
-      <c r="AV24" s="65" t="s">
+      <c r="AV24" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW24" s="65">
+      <c r="AW24" s="63">
         <v>256</v>
       </c>
       <c r="AX24" s="51">
@@ -5322,7 +5299,7 @@
     </row>
     <row r="25" s="3" customFormat="1" spans="1:55">
       <c r="A25" s="51" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B25" s="51" t="s">
         <v>107</v>
@@ -5330,104 +5307,104 @@
       <c r="C25" s="51">
         <v>1</v>
       </c>
-      <c r="D25" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>127</v>
+      <c r="D25" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F25" s="48">
         <v>800</v>
       </c>
       <c r="G25" s="48"/>
       <c r="H25" s="48"/>
-      <c r="I25" s="53" t="s">
-        <v>128</v>
+      <c r="I25" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J25" s="51">
         <v>1</v>
       </c>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="55"/>
-      <c r="Y25" s="55"/>
-      <c r="Z25" s="55"/>
-      <c r="AA25" s="57">
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="54"/>
+      <c r="U25" s="54"/>
+      <c r="V25" s="54"/>
+      <c r="W25" s="54"/>
+      <c r="X25" s="54"/>
+      <c r="Y25" s="54"/>
+      <c r="Z25" s="54"/>
+      <c r="AA25" s="56">
         <v>75</v>
       </c>
-      <c r="AB25" s="57">
+      <c r="AB25" s="56">
         <v>20</v>
       </c>
-      <c r="AC25" s="55">
+      <c r="AC25" s="54">
         <v>650</v>
       </c>
-      <c r="AD25" s="55">
+      <c r="AD25" s="54">
         <v>0</v>
       </c>
-      <c r="AE25" s="55">
+      <c r="AE25" s="54">
         <v>75</v>
       </c>
-      <c r="AF25" s="55">
+      <c r="AF25" s="54">
         <v>0</v>
       </c>
-      <c r="AG25" s="55" t="s">
+      <c r="AG25" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH25" s="61">
+      <c r="AH25" s="59">
         <v>40</v>
       </c>
-      <c r="AI25" s="61">
+      <c r="AI25" s="59">
         <v>40</v>
       </c>
-      <c r="AJ25" s="61">
+      <c r="AJ25" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK25" s="61"/>
-      <c r="AL25" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM25" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN25" s="63">
+      <c r="AK25" s="59"/>
+      <c r="AL25" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM25" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN25" s="61">
         <v>500</v>
       </c>
-      <c r="AO25" s="63">
+      <c r="AO25" s="61">
         <v>10</v>
       </c>
-      <c r="AP25" s="65" t="s">
+      <c r="AP25" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ25" s="65" t="s">
+      <c r="AQ25" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR25" s="65" t="s">
+      <c r="AR25" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS25" s="65" t="s">
+      <c r="AS25" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT25" s="65">
+      <c r="AT25" s="63">
         <v>900</v>
       </c>
-      <c r="AU25" s="65">
+      <c r="AU25" s="63">
         <v>600</v>
       </c>
-      <c r="AV25" s="65" t="s">
+      <c r="AV25" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW25" s="65">
+      <c r="AW25" s="63">
         <v>256</v>
       </c>
       <c r="AX25" s="51">
@@ -5449,7 +5426,7 @@
     </row>
     <row r="26" s="3" customFormat="1" spans="1:55">
       <c r="A26" s="51" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B26" s="51" t="s">
         <v>107</v>
@@ -5457,104 +5434,104 @@
       <c r="C26" s="51">
         <v>1</v>
       </c>
-      <c r="D26" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>127</v>
+      <c r="D26" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F26" s="48">
         <v>800</v>
       </c>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
-      <c r="I26" s="53" t="s">
-        <v>128</v>
+      <c r="I26" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J26" s="51">
         <v>1</v>
       </c>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="55"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="55"/>
-      <c r="X26" s="55"/>
-      <c r="Y26" s="55"/>
-      <c r="Z26" s="55"/>
-      <c r="AA26" s="57">
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="54"/>
+      <c r="U26" s="54"/>
+      <c r="V26" s="54"/>
+      <c r="W26" s="54"/>
+      <c r="X26" s="54"/>
+      <c r="Y26" s="54"/>
+      <c r="Z26" s="54"/>
+      <c r="AA26" s="56">
         <v>40</v>
       </c>
-      <c r="AB26" s="57">
+      <c r="AB26" s="56">
         <v>20</v>
       </c>
-      <c r="AC26" s="55">
+      <c r="AC26" s="54">
         <v>750</v>
       </c>
-      <c r="AD26" s="55">
+      <c r="AD26" s="54">
         <v>0</v>
       </c>
-      <c r="AE26" s="55">
+      <c r="AE26" s="54">
         <v>125</v>
       </c>
-      <c r="AF26" s="55">
+      <c r="AF26" s="54">
         <v>50</v>
       </c>
-      <c r="AG26" s="55" t="s">
+      <c r="AG26" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH26" s="61">
+      <c r="AH26" s="59">
         <v>70</v>
       </c>
-      <c r="AI26" s="61">
+      <c r="AI26" s="59">
         <v>70</v>
       </c>
-      <c r="AJ26" s="61">
-        <v>1</v>
-      </c>
-      <c r="AK26" s="61"/>
-      <c r="AL26" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM26" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN26" s="63">
+      <c r="AJ26" s="59">
+        <v>1</v>
+      </c>
+      <c r="AK26" s="59"/>
+      <c r="AL26" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM26" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN26" s="61">
         <v>500</v>
       </c>
-      <c r="AO26" s="63">
+      <c r="AO26" s="61">
         <v>10</v>
       </c>
-      <c r="AP26" s="65" t="s">
+      <c r="AP26" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ26" s="65" t="s">
+      <c r="AQ26" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR26" s="65" t="s">
+      <c r="AR26" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS26" s="65" t="s">
+      <c r="AS26" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT26" s="65">
+      <c r="AT26" s="63">
         <v>900</v>
       </c>
-      <c r="AU26" s="65">
+      <c r="AU26" s="63">
         <v>600</v>
       </c>
-      <c r="AV26" s="65" t="s">
+      <c r="AV26" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW26" s="65">
+      <c r="AW26" s="63">
         <v>256</v>
       </c>
       <c r="AX26" s="51">
@@ -5576,7 +5553,7 @@
     </row>
     <row r="27" s="3" customFormat="1" spans="1:55">
       <c r="A27" s="51" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>107</v>
@@ -5584,104 +5561,104 @@
       <c r="C27" s="51">
         <v>1</v>
       </c>
-      <c r="D27" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" s="53" t="s">
-        <v>127</v>
+      <c r="D27" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F27" s="48">
         <v>800</v>
       </c>
       <c r="G27" s="48"/>
       <c r="H27" s="48"/>
-      <c r="I27" s="53" t="s">
-        <v>128</v>
+      <c r="I27" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J27" s="51">
         <v>1</v>
       </c>
-      <c r="K27" s="55"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="55"/>
-      <c r="Q27" s="55"/>
-      <c r="R27" s="55"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="55"/>
-      <c r="U27" s="55"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="55"/>
-      <c r="X27" s="55"/>
-      <c r="Y27" s="55"/>
-      <c r="Z27" s="55"/>
-      <c r="AA27" s="57">
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
+      <c r="R27" s="54"/>
+      <c r="S27" s="54"/>
+      <c r="T27" s="54"/>
+      <c r="U27" s="54"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="54"/>
+      <c r="X27" s="54"/>
+      <c r="Y27" s="54"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="56">
         <v>20</v>
       </c>
-      <c r="AB27" s="57">
+      <c r="AB27" s="56">
         <v>20</v>
       </c>
-      <c r="AC27" s="55">
+      <c r="AC27" s="54">
         <v>500</v>
       </c>
-      <c r="AD27" s="55">
+      <c r="AD27" s="54">
         <v>0</v>
       </c>
-      <c r="AE27" s="55">
+      <c r="AE27" s="54">
         <v>95</v>
       </c>
-      <c r="AF27" s="55">
+      <c r="AF27" s="54">
         <v>0</v>
       </c>
-      <c r="AG27" s="55" t="s">
+      <c r="AG27" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH27" s="61">
+      <c r="AH27" s="59">
         <v>40</v>
       </c>
-      <c r="AI27" s="61">
+      <c r="AI27" s="59">
         <v>40</v>
       </c>
-      <c r="AJ27" s="61">
+      <c r="AJ27" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK27" s="61"/>
-      <c r="AL27" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM27" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN27" s="63">
+      <c r="AK27" s="59"/>
+      <c r="AL27" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM27" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN27" s="61">
         <v>500</v>
       </c>
-      <c r="AO27" s="63">
+      <c r="AO27" s="61">
         <v>10</v>
       </c>
-      <c r="AP27" s="65" t="s">
+      <c r="AP27" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ27" s="65" t="s">
+      <c r="AQ27" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR27" s="65" t="s">
+      <c r="AR27" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS27" s="65" t="s">
+      <c r="AS27" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT27" s="65">
+      <c r="AT27" s="63">
         <v>900</v>
       </c>
-      <c r="AU27" s="65">
+      <c r="AU27" s="63">
         <v>600</v>
       </c>
-      <c r="AV27" s="65" t="s">
+      <c r="AV27" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW27" s="65">
+      <c r="AW27" s="63">
         <v>256</v>
       </c>
       <c r="AX27" s="51">
@@ -5703,7 +5680,7 @@
     </row>
     <row r="28" s="3" customFormat="1" spans="1:55">
       <c r="A28" s="51" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>107</v>
@@ -5711,104 +5688,104 @@
       <c r="C28" s="51">
         <v>1</v>
       </c>
-      <c r="D28" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>127</v>
+      <c r="D28" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F28" s="48">
         <v>800</v>
       </c>
       <c r="G28" s="48"/>
       <c r="H28" s="48"/>
-      <c r="I28" s="53" t="s">
-        <v>128</v>
+      <c r="I28" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J28" s="51">
         <v>1</v>
       </c>
-      <c r="K28" s="55"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="55"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="55"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="55"/>
-      <c r="Y28" s="55"/>
-      <c r="Z28" s="55"/>
-      <c r="AA28" s="57">
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="54"/>
+      <c r="W28" s="54"/>
+      <c r="X28" s="54"/>
+      <c r="Y28" s="54"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="56">
         <v>40</v>
       </c>
-      <c r="AB28" s="57">
+      <c r="AB28" s="56">
         <v>20</v>
       </c>
-      <c r="AC28" s="55">
+      <c r="AC28" s="54">
         <v>700</v>
       </c>
-      <c r="AD28" s="55">
+      <c r="AD28" s="54">
         <v>0</v>
       </c>
-      <c r="AE28" s="55">
+      <c r="AE28" s="54">
         <v>75</v>
       </c>
-      <c r="AF28" s="55">
+      <c r="AF28" s="54">
         <v>0</v>
       </c>
-      <c r="AG28" s="55" t="s">
+      <c r="AG28" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH28" s="61">
+      <c r="AH28" s="59">
         <v>50</v>
       </c>
-      <c r="AI28" s="61">
+      <c r="AI28" s="59">
         <v>50</v>
       </c>
-      <c r="AJ28" s="61">
+      <c r="AJ28" s="59">
         <v>0.5</v>
       </c>
-      <c r="AK28" s="61"/>
-      <c r="AL28" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM28" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN28" s="63">
+      <c r="AK28" s="59"/>
+      <c r="AL28" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM28" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN28" s="61">
         <v>500</v>
       </c>
-      <c r="AO28" s="63">
+      <c r="AO28" s="61">
         <v>10</v>
       </c>
-      <c r="AP28" s="65" t="s">
+      <c r="AP28" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ28" s="65" t="s">
+      <c r="AQ28" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR28" s="65" t="s">
+      <c r="AR28" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS28" s="65" t="s">
+      <c r="AS28" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT28" s="65">
+      <c r="AT28" s="63">
         <v>900</v>
       </c>
-      <c r="AU28" s="65">
+      <c r="AU28" s="63">
         <v>600</v>
       </c>
-      <c r="AV28" s="65" t="s">
+      <c r="AV28" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW28" s="65">
+      <c r="AW28" s="63">
         <v>256</v>
       </c>
       <c r="AX28" s="51">
@@ -5830,7 +5807,7 @@
     </row>
     <row r="29" s="3" customFormat="1" spans="1:55">
       <c r="A29" s="51" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>107</v>
@@ -5838,104 +5815,104 @@
       <c r="C29" s="51">
         <v>1</v>
       </c>
-      <c r="D29" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="53" t="s">
-        <v>127</v>
+      <c r="D29" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F29" s="48">
         <v>800</v>
       </c>
       <c r="G29" s="48"/>
       <c r="H29" s="48"/>
-      <c r="I29" s="53" t="s">
-        <v>128</v>
+      <c r="I29" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J29" s="51">
         <v>1</v>
       </c>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="55"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="55"/>
-      <c r="Z29" s="55"/>
-      <c r="AA29" s="57">
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="54"/>
+      <c r="V29" s="54"/>
+      <c r="W29" s="54"/>
+      <c r="X29" s="54"/>
+      <c r="Y29" s="54"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="56">
         <v>20</v>
       </c>
-      <c r="AB29" s="57">
+      <c r="AB29" s="56">
         <v>20</v>
       </c>
-      <c r="AC29" s="55">
+      <c r="AC29" s="54">
         <v>650</v>
       </c>
-      <c r="AD29" s="55">
+      <c r="AD29" s="54">
         <v>0</v>
       </c>
-      <c r="AE29" s="55">
+      <c r="AE29" s="54">
         <v>150</v>
       </c>
-      <c r="AF29" s="55">
+      <c r="AF29" s="54">
         <v>50</v>
       </c>
-      <c r="AG29" s="55" t="s">
+      <c r="AG29" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH29" s="61">
+      <c r="AH29" s="59">
         <v>50</v>
       </c>
-      <c r="AI29" s="61">
+      <c r="AI29" s="59">
         <v>50</v>
       </c>
-      <c r="AJ29" s="61">
+      <c r="AJ29" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK29" s="61"/>
-      <c r="AL29" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM29" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN29" s="63">
+      <c r="AK29" s="59"/>
+      <c r="AL29" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM29" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN29" s="61">
         <v>500</v>
       </c>
-      <c r="AO29" s="63">
+      <c r="AO29" s="61">
         <v>10</v>
       </c>
-      <c r="AP29" s="65" t="s">
+      <c r="AP29" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ29" s="65" t="s">
+      <c r="AQ29" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR29" s="65" t="s">
+      <c r="AR29" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS29" s="65" t="s">
+      <c r="AS29" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT29" s="65">
+      <c r="AT29" s="63">
         <v>900</v>
       </c>
-      <c r="AU29" s="65">
+      <c r="AU29" s="63">
         <v>600</v>
       </c>
-      <c r="AV29" s="65" t="s">
+      <c r="AV29" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW29" s="65">
+      <c r="AW29" s="63">
         <v>256</v>
       </c>
       <c r="AX29" s="51">
@@ -5957,7 +5934,7 @@
     </row>
     <row r="30" s="3" customFormat="1" spans="1:55">
       <c r="A30" s="51" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>107</v>
@@ -5965,104 +5942,104 @@
       <c r="C30" s="51">
         <v>1</v>
       </c>
-      <c r="D30" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>127</v>
+      <c r="D30" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F30" s="48">
         <v>800</v>
       </c>
       <c r="G30" s="48"/>
       <c r="H30" s="48"/>
-      <c r="I30" s="53" t="s">
-        <v>128</v>
+      <c r="I30" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J30" s="51">
         <v>1</v>
       </c>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="55"/>
-      <c r="V30" s="55"/>
-      <c r="W30" s="55"/>
-      <c r="X30" s="55"/>
-      <c r="Y30" s="55"/>
-      <c r="Z30" s="55"/>
-      <c r="AA30" s="57">
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="54"/>
+      <c r="R30" s="54"/>
+      <c r="S30" s="54"/>
+      <c r="T30" s="54"/>
+      <c r="U30" s="54"/>
+      <c r="V30" s="54"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="54"/>
+      <c r="Y30" s="54"/>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="56">
         <v>20</v>
       </c>
-      <c r="AB30" s="57">
+      <c r="AB30" s="56">
         <v>20</v>
       </c>
-      <c r="AC30" s="55">
+      <c r="AC30" s="54">
         <v>1000</v>
       </c>
-      <c r="AD30" s="55">
+      <c r="AD30" s="54">
         <v>0</v>
       </c>
-      <c r="AE30" s="55">
+      <c r="AE30" s="54">
         <v>150</v>
       </c>
-      <c r="AF30" s="55">
+      <c r="AF30" s="54">
         <v>50</v>
       </c>
-      <c r="AG30" s="55" t="s">
+      <c r="AG30" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH30" s="61">
+      <c r="AH30" s="59">
         <v>70</v>
       </c>
-      <c r="AI30" s="61">
+      <c r="AI30" s="59">
         <v>70</v>
       </c>
-      <c r="AJ30" s="61">
+      <c r="AJ30" s="59">
         <v>0.6</v>
       </c>
-      <c r="AK30" s="61"/>
-      <c r="AL30" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM30" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN30" s="63">
+      <c r="AK30" s="59"/>
+      <c r="AL30" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM30" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN30" s="61">
         <v>500</v>
       </c>
-      <c r="AO30" s="63">
+      <c r="AO30" s="61">
         <v>10</v>
       </c>
-      <c r="AP30" s="65" t="s">
+      <c r="AP30" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ30" s="65" t="s">
+      <c r="AQ30" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR30" s="65" t="s">
+      <c r="AR30" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS30" s="65" t="s">
+      <c r="AS30" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT30" s="65">
+      <c r="AT30" s="63">
         <v>900</v>
       </c>
-      <c r="AU30" s="65">
+      <c r="AU30" s="63">
         <v>600</v>
       </c>
-      <c r="AV30" s="65" t="s">
+      <c r="AV30" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW30" s="65">
+      <c r="AW30" s="63">
         <v>256</v>
       </c>
       <c r="AX30" s="51">
@@ -6084,7 +6061,7 @@
     </row>
     <row r="31" s="3" customFormat="1" spans="1:55">
       <c r="A31" s="51" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B31" s="51" t="s">
         <v>107</v>
@@ -6092,104 +6069,104 @@
       <c r="C31" s="51">
         <v>1</v>
       </c>
-      <c r="D31" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="53" t="s">
-        <v>127</v>
+      <c r="D31" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="F31" s="48">
         <v>800</v>
       </c>
       <c r="G31" s="48"/>
       <c r="H31" s="48"/>
-      <c r="I31" s="53" t="s">
-        <v>128</v>
+      <c r="I31" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="J31" s="51">
         <v>1</v>
       </c>
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="55"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="55"/>
-      <c r="V31" s="55"/>
-      <c r="W31" s="55"/>
-      <c r="X31" s="55"/>
-      <c r="Y31" s="55"/>
-      <c r="Z31" s="55"/>
-      <c r="AA31" s="57">
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="54"/>
+      <c r="N31" s="54"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="54"/>
+      <c r="R31" s="54"/>
+      <c r="S31" s="54"/>
+      <c r="T31" s="54"/>
+      <c r="U31" s="54"/>
+      <c r="V31" s="54"/>
+      <c r="W31" s="54"/>
+      <c r="X31" s="54"/>
+      <c r="Y31" s="54"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="56">
         <v>35</v>
       </c>
-      <c r="AB31" s="57">
+      <c r="AB31" s="56">
         <v>20</v>
       </c>
-      <c r="AC31" s="55">
+      <c r="AC31" s="54">
         <v>750</v>
       </c>
-      <c r="AD31" s="55">
+      <c r="AD31" s="54">
         <v>0</v>
       </c>
-      <c r="AE31" s="55">
+      <c r="AE31" s="54">
         <v>25</v>
       </c>
-      <c r="AF31" s="55">
+      <c r="AF31" s="54">
         <v>0</v>
       </c>
-      <c r="AG31" s="55" t="s">
+      <c r="AG31" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="AH31" s="61">
+      <c r="AH31" s="59">
         <v>75</v>
       </c>
-      <c r="AI31" s="61">
+      <c r="AI31" s="59">
         <v>75</v>
       </c>
-      <c r="AJ31" s="61">
-        <v>1</v>
-      </c>
-      <c r="AK31" s="61"/>
-      <c r="AL31" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM31" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN31" s="63">
+      <c r="AJ31" s="59">
+        <v>1</v>
+      </c>
+      <c r="AK31" s="59"/>
+      <c r="AL31" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM31" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN31" s="61">
         <v>500</v>
       </c>
-      <c r="AO31" s="63">
+      <c r="AO31" s="61">
         <v>10</v>
       </c>
-      <c r="AP31" s="65" t="s">
+      <c r="AP31" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="AQ31" s="65" t="s">
+      <c r="AQ31" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="AR31" s="65" t="s">
+      <c r="AR31" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AS31" s="65" t="s">
+      <c r="AS31" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="AT31" s="65">
+      <c r="AT31" s="63">
         <v>900</v>
       </c>
-      <c r="AU31" s="65">
+      <c r="AU31" s="63">
         <v>600</v>
       </c>
-      <c r="AV31" s="65" t="s">
+      <c r="AV31" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="AW31" s="65">
+      <c r="AW31" s="63">
         <v>256</v>
       </c>
       <c r="AX31" s="51">
@@ -6230,16 +6207,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="34" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6256,13 +6233,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="35" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -6271,7 +6248,7 @@
         <v>54</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
@@ -6295,7 +6272,7 @@
         <v>81</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
@@ -6319,7 +6296,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3">
         <v>3</v>
@@ -6370,10 +6347,10 @@
         <v>37</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6402,10 +6379,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="35" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C15" s="3">
         <v>110</v>
@@ -6438,10 +6415,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="35" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C18" s="3">
         <v>900</v>
@@ -6453,11 +6430,11 @@
         <v>56</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="34" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6465,7 +6442,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C20" s="3">
         <v>1000</v>
@@ -6477,7 +6454,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C21" s="3">
         <v>0.3</v>
@@ -6492,10 +6469,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -6515,13 +6492,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6529,7 +6506,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C25" s="3">
         <v>1200</v>
@@ -6541,7 +6518,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C26" s="3">
         <v>1000</v>
@@ -6550,10 +6527,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C27" s="3">
         <v>50</v>
@@ -6562,10 +6539,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="35" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C28" s="3">
         <v>40</v>
@@ -6574,10 +6551,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="35" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C29" s="3">
         <v>20</v>
@@ -6586,10 +6563,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="35" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -6599,7 +6576,7 @@
         <v>102</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
@@ -6611,11 +6588,11 @@
         <v>105</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="34" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -6623,7 +6600,7 @@
         <v>103</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -6633,67 +6610,67 @@
         <v>101</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="35" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="35" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="35" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="35" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="35" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="35" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -6720,10 +6697,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="35" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -6733,17 +6710,17 @@
         <v>60</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="35" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -6753,19 +6730,19 @@
         <v>59</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D46" s="3"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="35" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -6792,20 +6769,20 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="35" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="35" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -6866,10 +6843,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>1</v>
@@ -6878,16 +6855,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
@@ -6902,16 +6879,16 @@
       <c r="T1" s="12"/>
       <c r="U1" s="12"/>
       <c r="V1" s="12" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="W1" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="X1" s="17" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
@@ -6920,28 +6897,28 @@
       <c r="AD1" s="20"/>
       <c r="AE1" s="20"/>
       <c r="AF1" s="20" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG1" s="23" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AH1" s="10" t="s">
         <v>39</v>
       </c>
       <c r="AI1" s="24" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AJ1" s="25" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AK1" s="10" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AL1" s="26" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN1" s="10" t="s">
         <v>27</v>
@@ -6950,57 +6927,57 @@
         <v>28</v>
       </c>
       <c r="AP1" s="10" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AQ1" s="10" t="s">
         <v>30</v>
       </c>
       <c r="AR1" s="10" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AS1" s="10" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AT1" s="10" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="AU1" s="26" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AV1" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AW1" s="26" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AX1" s="32" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AY1" s="26" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AZ1" s="26" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="BA1" s="26" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="BB1" s="33" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="BC1" s="33" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="BD1" s="33" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="BE1" s="33" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="36.75" customHeight="1" spans="1:57">
       <c r="A2" s="9" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -7011,16 +6988,16 @@
         <v>55</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="J2" s="12">
         <v>1</v>
@@ -7053,22 +7030,22 @@
         <v>10</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="V2" s="12" t="s">
         <v>59</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="X2" s="17" t="s">
         <v>60</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Z2" s="20" t="s">
         <v>62</v>
@@ -7101,7 +7078,7 @@
         <v>92</v>
       </c>
       <c r="AJ2" s="25" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AK2" s="10" t="s">
         <v>90</v>
@@ -7128,10 +7105,10 @@
         <v>84</v>
       </c>
       <c r="AS2" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AT2" s="10" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AU2" s="26" t="s">
         <v>85</v>
@@ -7149,7 +7126,7 @@
         <v>88</v>
       </c>
       <c r="AZ2" s="26" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>104</v>
@@ -7161,7 +7138,7 @@
         <v>57</v>
       </c>
       <c r="BD2" s="33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="BE2" s="33" t="s">
         <v>102</v>
@@ -7169,10 +7146,10 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:57">
       <c r="A3" s="13" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C3" s="13" t="str">
         <f>SUBSTITUTE(B3,"npc_dota_hero_","")</f>
@@ -7182,7 +7159,7 @@
         <v>107</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="14">
@@ -7207,14 +7184,14 @@
       <c r="T3" s="14"/>
       <c r="U3" s="14"/>
       <c r="V3" s="14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="W3" s="14"/>
       <c r="X3" s="18" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Y3" s="18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Z3" s="21"/>
       <c r="AA3" s="18"/>
@@ -7241,7 +7218,7 @@
         <v>#REF!</v>
       </c>
       <c r="AK3" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AL3" s="18" t="e">
         <f>VLOOKUP("npc_dota_hero_"&amp;$C3,#REF!,19,FALSE)</f>
@@ -7287,7 +7264,7 @@
         <v>130</v>
       </c>
       <c r="AZ3" s="18" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="BA3" s="14">
         <v>70</v>

--- a/excels/单位表.xlsx
+++ b/excels/单位表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProject\FusionDota\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8735304-24A0-4FA1-A5E6-B6A20D9E7F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="15350" windowHeight="24880"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="custom_units" sheetId="1" r:id="rId1"/>
@@ -23,9 +29,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -416,441 +423,465 @@
 </t>
   </si>
   <si>
+    <t>models/heroes/windrunner/windrunner.vmdl</t>
+  </si>
+  <si>
+    <t>particles/units/heroes/hero_windrunner\windrunner_base_attack.vpcf</t>
+  </si>
+  <si>
+    <t>Hero_Windrunner</t>
+  </si>
+  <si>
+    <t>soundevents/game_sounds_heroes/game_sounds_windrunner.vsndevts</t>
+  </si>
+  <si>
+    <t>windrunner_powershot</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_RANGED_ATTACK</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_MOVE_GROUND</t>
+  </si>
+  <si>
+    <t>models/heroes/</t>
+  </si>
+  <si>
+    <t>particles/units/heroes/</t>
+  </si>
+  <si>
+    <t>soundevents/</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_MELEE_ATTACK</t>
+  </si>
+  <si>
+    <t>键值</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>示例</t>
+  </si>
+  <si>
+    <t>vscripts</t>
+  </si>
+  <si>
+    <t>AI脚本</t>
+  </si>
+  <si>
+    <t>scripts/vscripts/ai/ai_test.lua</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>生命值恢复</t>
+  </si>
+  <si>
+    <t>魔法值恢复</t>
+  </si>
+  <si>
+    <t>请到ts的UnitAttackCapability查看可用数值</t>
+  </si>
+  <si>
+    <t>BaseAttackSpeed</t>
+  </si>
+  <si>
+    <t>基础攻击速度</t>
+  </si>
+  <si>
+    <t>AttackRangeBuffer</t>
+  </si>
+  <si>
+    <t>攻击缓冲距离</t>
+  </si>
+  <si>
+    <t>投射物特效</t>
+  </si>
+  <si>
+    <t>所有的弹道类特效均可</t>
+  </si>
+  <si>
+    <t>投射物速度</t>
+  </si>
+  <si>
+    <t>攻击动画点</t>
+  </si>
+  <si>
+    <t>DOTA_UNIT_CAP_MOVE_FLY</t>
+  </si>
+  <si>
+    <t>请到ts的UnitMoveCapability查看可用数值</t>
+  </si>
+  <si>
+    <t>转身速度</t>
+  </si>
+  <si>
+    <t>转一圈所需要的时间</t>
+  </si>
+  <si>
+    <t>日间视野范围</t>
+  </si>
+  <si>
+    <t>夜间视野范围</t>
+  </si>
+  <si>
+    <t>BountyGoldMin</t>
+  </si>
+  <si>
+    <t>最大赏金</t>
+  </si>
+  <si>
+    <t>BountyGoldMax</t>
+  </si>
+  <si>
+    <t>最小赏金</t>
+  </si>
+  <si>
+    <t>BountyXP</t>
+  </si>
+  <si>
+    <t>击杀经验值</t>
+  </si>
+  <si>
+    <t>Ability1-Ability32</t>
+  </si>
+  <si>
+    <t>技能们</t>
+  </si>
+  <si>
+    <t>是否拥有物品栏</t>
+  </si>
+  <si>
+    <t>该模块主要用于添加饰品</t>
+  </si>
+  <si>
+    <t>请参阅minions表</t>
+  </si>
+  <si>
+    <t>血条偏移距离</t>
+  </si>
+  <si>
+    <t>是否视为英雄</t>
+  </si>
+  <si>
+    <t>IsAncient</t>
+  </si>
+  <si>
+    <t>是否为远古</t>
+  </si>
+  <si>
+    <t>IsBoss</t>
+  </si>
+  <si>
+    <t>是否为BOSS</t>
+  </si>
+  <si>
+    <t>IsNeutralUnitType</t>
+  </si>
+  <si>
+    <t>是否为野怪</t>
+  </si>
+  <si>
+    <t>IsOther</t>
+  </si>
+  <si>
+    <t>是否为其他（墓碑等）</t>
+  </si>
+  <si>
+    <t>IsRoshan</t>
+  </si>
+  <si>
+    <t>是否为肉山</t>
+  </si>
+  <si>
+    <t>IsSummoned</t>
+  </si>
+  <si>
+    <t>是否为召唤物</t>
+  </si>
+  <si>
+    <t>precache</t>
+  </si>
+  <si>
+    <t>预载</t>
+  </si>
+  <si>
+    <t>音效文件</t>
+  </si>
+  <si>
+    <t>VoiceFile</t>
+  </si>
+  <si>
+    <t>配音文件</t>
+  </si>
+  <si>
+    <t>声音设置</t>
+  </si>
+  <si>
+    <t>Hero_Sniper</t>
+  </si>
+  <si>
+    <t>particle_folder</t>
+  </si>
+  <si>
+    <t>特效文件夹</t>
+  </si>
+  <si>
+    <t>Skin</t>
+  </si>
+  <si>
+    <t>皮肤</t>
+  </si>
+  <si>
+    <t>DisableWearables</t>
+  </si>
+  <si>
+    <t>是否禁用饰品</t>
+  </si>
+  <si>
+    <t>对应英雄</t>
+  </si>
+  <si>
+    <t>纯英雄名字</t>
+  </si>
+  <si>
+    <t>模型尺寸</t>
+  </si>
+  <si>
+    <t>特殊数据</t>
+  </si>
+  <si>
+    <t>挂载饰品</t>
+  </si>
+  <si>
+    <t>粒子目录</t>
+  </si>
+  <si>
+    <t>声音文件</t>
+  </si>
+  <si>
+    <t>语音文件</t>
+  </si>
+  <si>
+    <t>英雄血条</t>
+  </si>
+  <si>
+    <t>血条高度</t>
+  </si>
+  <si>
+    <t>攻击姿态</t>
+  </si>
+  <si>
+    <t>移动类型</t>
+  </si>
+  <si>
+    <t>护甲值</t>
+  </si>
+  <si>
+    <t>生命恢复</t>
+  </si>
+  <si>
+    <t>魔法恢复</t>
+  </si>
+  <si>
+    <t>最小击杀金钱</t>
+  </si>
+  <si>
+    <t>最大击杀金钱</t>
+  </si>
+  <si>
+    <t>最小攻击</t>
+  </si>
+  <si>
+    <t>最大攻击</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
+    <t>攻击前摇</t>
+  </si>
+  <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
+    <t>碰撞体积</t>
+  </si>
+  <si>
+    <t>选取框半径</t>
+  </si>
+  <si>
+    <t>投射物速率</t>
+  </si>
+  <si>
+    <t>AI文件</t>
+  </si>
+  <si>
+    <t>是否有背包</t>
+  </si>
+  <si>
+    <t>UnitName</t>
+  </si>
+  <si>
+    <t>Creature[{]</t>
+  </si>
+  <si>
+    <t>AttachWearables[{]</t>
+  </si>
+  <si>
+    <t>[}]</t>
+  </si>
+  <si>
+    <t>HasAggressiveStance</t>
+  </si>
+  <si>
+    <t>BoundsHullName</t>
+  </si>
+  <si>
+    <t>npc_kv_custom_earthshaker</t>
+  </si>
+  <si>
+    <t>npc_dota_hero_earthshaker</t>
+  </si>
+  <si>
+    <t>models/heroes/earthshaker/earthshaker.vmdl</t>
+  </si>
+  <si>
+    <t>Hero_EarthShaker</t>
+  </si>
+  <si>
+    <t>soundevents/game_sounds_heroes/game_sounds_earthshaker.vsndevts</t>
+  </si>
+  <si>
+    <t>soundevents/voscripts/game_sounds_vo_earthshaker.vsndevts</t>
+  </si>
+  <si>
+    <t>DOTA_HULL_SIZE_HERO</t>
+  </si>
+  <si>
+    <t>monster1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster6</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster7</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster8</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster9</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster10</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster11</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster12</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster13</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster14</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster15</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster16</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster17</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster18</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster19</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster20</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster21</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster22</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster23</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster24</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster25</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster26</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster27</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>windrunner</t>
-  </si>
-  <si>
-    <t>models/heroes/windrunner/windrunner.vmdl</t>
-  </si>
-  <si>
-    <t>particles/units/heroes/hero_windrunner\windrunner_base_attack.vpcf</t>
-  </si>
-  <si>
-    <t>Hero_Windrunner</t>
-  </si>
-  <si>
-    <t>soundevents/game_sounds_heroes/game_sounds_windrunner.vsndevts</t>
-  </si>
-  <si>
-    <t>windrunner_powershot</t>
-  </si>
-  <si>
-    <t>DOTA_UNIT_CAP_RANGED_ATTACK</t>
-  </si>
-  <si>
-    <t>DOTA_UNIT_CAP_MOVE_GROUND</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 格雷福斯</t>
-  </si>
-  <si>
-    <t>models/heroes/</t>
-  </si>
-  <si>
-    <t>particles/units/heroes/</t>
-  </si>
-  <si>
-    <t>soundevents/</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 卢锡安</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 慎</t>
-  </si>
-  <si>
-    <t>DOTA_UNIT_CAP_MELEE_ATTACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 普朗克</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 金克丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 厄运小姐</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 薇恩</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 崔斯特</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 韦鲁斯</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 艾希</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 千珏</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 卡莎</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 伊莉丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 莫甘娜</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 伊芙琳</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 布兰德</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 斯维因</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 盖伦</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 菲奥娜</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 蕾欧娜</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 布隆</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 凯尔</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 丽桑卓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 波比</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 雷克塞</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 科加斯</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 亚索</t>
-  </si>
-  <si>
-    <t>键值</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>vscripts</t>
-  </si>
-  <si>
-    <t>AI脚本</t>
-  </si>
-  <si>
-    <t>scripts/vscripts/ai/ai_test.lua</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>生命值恢复</t>
-  </si>
-  <si>
-    <t>魔法值恢复</t>
-  </si>
-  <si>
-    <t>请到ts的UnitAttackCapability查看可用数值</t>
-  </si>
-  <si>
-    <t>BaseAttackSpeed</t>
-  </si>
-  <si>
-    <t>基础攻击速度</t>
-  </si>
-  <si>
-    <t>AttackRangeBuffer</t>
-  </si>
-  <si>
-    <t>攻击缓冲距离</t>
-  </si>
-  <si>
-    <t>投射物特效</t>
-  </si>
-  <si>
-    <t>所有的弹道类特效均可</t>
-  </si>
-  <si>
-    <t>投射物速度</t>
-  </si>
-  <si>
-    <t>攻击动画点</t>
-  </si>
-  <si>
-    <t>DOTA_UNIT_CAP_MOVE_FLY</t>
-  </si>
-  <si>
-    <t>请到ts的UnitMoveCapability查看可用数值</t>
-  </si>
-  <si>
-    <t>转身速度</t>
-  </si>
-  <si>
-    <t>转一圈所需要的时间</t>
-  </si>
-  <si>
-    <t>日间视野范围</t>
-  </si>
-  <si>
-    <t>夜间视野范围</t>
-  </si>
-  <si>
-    <t>BountyGoldMin</t>
-  </si>
-  <si>
-    <t>最大赏金</t>
-  </si>
-  <si>
-    <t>BountyGoldMax</t>
-  </si>
-  <si>
-    <t>最小赏金</t>
-  </si>
-  <si>
-    <t>BountyXP</t>
-  </si>
-  <si>
-    <t>击杀经验值</t>
-  </si>
-  <si>
-    <t>Ability1-Ability32</t>
-  </si>
-  <si>
-    <t>技能们</t>
-  </si>
-  <si>
-    <t>是否拥有物品栏</t>
-  </si>
-  <si>
-    <t>该模块主要用于添加饰品</t>
-  </si>
-  <si>
-    <t>请参阅minions表</t>
-  </si>
-  <si>
-    <t>血条偏移距离</t>
-  </si>
-  <si>
-    <t>是否视为英雄</t>
-  </si>
-  <si>
-    <t>IsAncient</t>
-  </si>
-  <si>
-    <t>是否为远古</t>
-  </si>
-  <si>
-    <t>IsBoss</t>
-  </si>
-  <si>
-    <t>是否为BOSS</t>
-  </si>
-  <si>
-    <t>IsNeutralUnitType</t>
-  </si>
-  <si>
-    <t>是否为野怪</t>
-  </si>
-  <si>
-    <t>IsOther</t>
-  </si>
-  <si>
-    <t>是否为其他（墓碑等）</t>
-  </si>
-  <si>
-    <t>IsRoshan</t>
-  </si>
-  <si>
-    <t>是否为肉山</t>
-  </si>
-  <si>
-    <t>IsSummoned</t>
-  </si>
-  <si>
-    <t>是否为召唤物</t>
-  </si>
-  <si>
-    <t>precache</t>
-  </si>
-  <si>
-    <t>预载</t>
-  </si>
-  <si>
-    <t>音效文件</t>
-  </si>
-  <si>
-    <t>VoiceFile</t>
-  </si>
-  <si>
-    <t>配音文件</t>
-  </si>
-  <si>
-    <t>声音设置</t>
-  </si>
-  <si>
-    <t>Hero_Sniper</t>
-  </si>
-  <si>
-    <t>particle_folder</t>
-  </si>
-  <si>
-    <t>特效文件夹</t>
-  </si>
-  <si>
-    <t>Skin</t>
-  </si>
-  <si>
-    <t>皮肤</t>
-  </si>
-  <si>
-    <t>DisableWearables</t>
-  </si>
-  <si>
-    <t>是否禁用饰品</t>
-  </si>
-  <si>
-    <t>对应英雄</t>
-  </si>
-  <si>
-    <t>纯英雄名字</t>
-  </si>
-  <si>
-    <t>模型尺寸</t>
-  </si>
-  <si>
-    <t>特殊数据</t>
-  </si>
-  <si>
-    <t>挂载饰品</t>
-  </si>
-  <si>
-    <t>粒子目录</t>
-  </si>
-  <si>
-    <t>声音文件</t>
-  </si>
-  <si>
-    <t>语音文件</t>
-  </si>
-  <si>
-    <t>英雄血条</t>
-  </si>
-  <si>
-    <t>血条高度</t>
-  </si>
-  <si>
-    <t>攻击姿态</t>
-  </si>
-  <si>
-    <t>移动类型</t>
-  </si>
-  <si>
-    <t>护甲值</t>
-  </si>
-  <si>
-    <t>生命恢复</t>
-  </si>
-  <si>
-    <t>魔法恢复</t>
-  </si>
-  <si>
-    <t>最小击杀金钱</t>
-  </si>
-  <si>
-    <t>最大击杀金钱</t>
-  </si>
-  <si>
-    <t>最小攻击</t>
-  </si>
-  <si>
-    <t>最大攻击</t>
-  </si>
-  <si>
-    <t>攻击间隔</t>
-  </si>
-  <si>
-    <t>攻击前摇</t>
-  </si>
-  <si>
-    <t>攻击范围</t>
-  </si>
-  <si>
-    <t>碰撞体积</t>
-  </si>
-  <si>
-    <t>选取框半径</t>
-  </si>
-  <si>
-    <t>投射物速率</t>
-  </si>
-  <si>
-    <t>AI文件</t>
-  </si>
-  <si>
-    <t>是否有背包</t>
-  </si>
-  <si>
-    <t>UnitName</t>
-  </si>
-  <si>
-    <t>Creature[{]</t>
-  </si>
-  <si>
-    <t>AttachWearables[{]</t>
-  </si>
-  <si>
-    <t>[}]</t>
-  </si>
-  <si>
-    <t>HasAggressiveStance</t>
-  </si>
-  <si>
-    <t>BoundsHullName</t>
-  </si>
-  <si>
-    <t>npc_kv_custom_earthshaker</t>
-  </si>
-  <si>
-    <t>npc_dota_hero_earthshaker</t>
-  </si>
-  <si>
-    <t>models/heroes/earthshaker/earthshaker.vmdl</t>
-  </si>
-  <si>
-    <t>Hero_EarthShaker</t>
-  </si>
-  <si>
-    <t>soundevents/game_sounds_heroes/game_sounds_earthshaker.vsndevts</t>
-  </si>
-  <si>
-    <t>soundevents/voscripts/game_sounds_vo_earthshaker.vsndevts</t>
-  </si>
-  <si>
-    <t>DOTA_HULL_SIZE_HERO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,151 +930,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1052,25 +954,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799829096346934"/>
+        <fgColor theme="7" tint="0.79979857783745845"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399822992645039"/>
+        <fgColor theme="6" tint="0.39979247413556324"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399822992645039"/>
+        <fgColor theme="5" tint="0.39979247413556324"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1082,7 +984,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799829096346934"/>
+        <fgColor theme="9" tint="0.79979857783745845"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1100,204 +1002,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1333,253 +1079,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1749,59 +1253,21 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="39">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1812,7 +1278,140 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.0499893185216834"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
       <border>
@@ -1823,19 +1422,93 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="-0.249946592608417"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1844,6 +1517,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2101,51 +1777,51 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:BC31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:XEQ31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="20.5666666666667" style="39" customWidth="1"/>
+    <col min="1" max="3" width="20.625" style="39" customWidth="1"/>
     <col min="4" max="4" width="37.75" style="40" customWidth="1"/>
-    <col min="5" max="5" width="47.175" style="41" customWidth="1"/>
-    <col min="6" max="6" width="14.275" style="42" customWidth="1"/>
-    <col min="7" max="7" width="21.45" style="42" customWidth="1"/>
-    <col min="8" max="8" width="15.075" style="42" customWidth="1"/>
-    <col min="9" max="9" width="51.8833333333333" style="41" customWidth="1"/>
-    <col min="10" max="10" width="9.14166666666667" style="39"/>
-    <col min="11" max="13" width="13.6416666666667" style="43" customWidth="1"/>
-    <col min="14" max="25" width="13.6416666666667" style="43" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="13.6416666666667" style="43" customWidth="1"/>
-    <col min="27" max="28" width="9.14166666666667" style="44"/>
-    <col min="29" max="29" width="16.1583333333333" style="43" customWidth="1"/>
-    <col min="30" max="30" width="9.14166666666667" style="43"/>
+    <col min="5" max="5" width="47.125" style="41" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="42" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="42" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="42" customWidth="1"/>
+    <col min="9" max="9" width="51.875" style="41" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="39"/>
+    <col min="11" max="13" width="13.625" style="43" customWidth="1"/>
+    <col min="14" max="25" width="13.625" style="43" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="13.625" style="43" customWidth="1"/>
+    <col min="27" max="28" width="9.125" style="44"/>
+    <col min="29" max="29" width="16.125" style="43" customWidth="1"/>
+    <col min="30" max="30" width="9.125" style="43"/>
     <col min="31" max="32" width="18.25" style="43" customWidth="1"/>
     <col min="33" max="33" width="16.5" style="43" customWidth="1"/>
-    <col min="34" max="34" width="14.0833333333333" style="45" customWidth="1"/>
-    <col min="35" max="35" width="16.9166666666667" style="45" customWidth="1"/>
-    <col min="36" max="36" width="15.0833333333333" style="45" customWidth="1"/>
-    <col min="37" max="37" width="9.14166666666667" style="45"/>
-    <col min="38" max="38" width="38.4166666666667" style="46" customWidth="1"/>
-    <col min="39" max="39" width="42.0833333333333" style="46" customWidth="1"/>
+    <col min="34" max="34" width="14.125" style="45" customWidth="1"/>
+    <col min="35" max="35" width="16.875" style="45" customWidth="1"/>
+    <col min="36" max="36" width="15.125" style="45" customWidth="1"/>
+    <col min="37" max="37" width="9.125" style="45"/>
+    <col min="38" max="38" width="38.375" style="46" customWidth="1"/>
+    <col min="39" max="39" width="42.125" style="46" customWidth="1"/>
     <col min="40" max="40" width="16.875" style="46" customWidth="1"/>
-    <col min="41" max="41" width="17.4666666666667" style="46" customWidth="1"/>
-    <col min="42" max="42" width="29.1333333333333" style="47" customWidth="1"/>
-    <col min="43" max="43" width="31.8083333333333" style="47" customWidth="1"/>
-    <col min="44" max="44" width="32.4666666666667" style="47" customWidth="1"/>
-    <col min="45" max="49" width="43.0416666666667" style="47" customWidth="1"/>
+    <col min="41" max="41" width="17.5" style="46" customWidth="1"/>
+    <col min="42" max="42" width="29.125" style="47" customWidth="1"/>
+    <col min="43" max="43" width="31.75" style="47" customWidth="1"/>
+    <col min="44" max="44" width="32.5" style="47" customWidth="1"/>
+    <col min="45" max="49" width="43" style="47" customWidth="1"/>
     <col min="50" max="53" width="17.75" style="39" customWidth="1"/>
-    <col min="54" max="54" width="18.7583333333333" style="39" customWidth="1"/>
-    <col min="55" max="55" width="30.0666666666667" style="48" customWidth="1"/>
-    <col min="56" max="16370" width="9.14166666666667" style="3"/>
+    <col min="54" max="54" width="18.75" style="39" customWidth="1"/>
+    <col min="55" max="55" width="30.125" style="48" customWidth="1"/>
+    <col min="56" max="16370" width="9.125" style="3"/>
     <col min="16372" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="38" customFormat="1" spans="1:55">
+    <row r="1" spans="1:55" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -2312,7 +1988,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" s="38" customFormat="1" spans="1:55">
+    <row r="2" spans="1:55" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49" t="s">
         <v>52</v>
       </c>
@@ -2479,7 +2155,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="56" spans="1:55">
+    <row r="3" spans="1:55" s="3" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A3" s="51" t="s">
         <v>106</v>
       </c>
@@ -2622,9 +2298,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:55">
-      <c r="A4" s="51" t="s">
-        <v>125</v>
+    <row r="4" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="65" t="s">
+        <v>265</v>
       </c>
       <c r="B4" s="51" t="s">
         <v>107</v>
@@ -2633,10 +2309,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="41" t="s">
         <v>126</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>127</v>
       </c>
       <c r="F4" s="48">
         <v>800</v>
@@ -2645,16 +2321,16 @@
         <v>0.4</v>
       </c>
       <c r="H4" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="J4" s="51">
+        <v>1</v>
+      </c>
+      <c r="K4" s="54" t="s">
         <v>129</v>
-      </c>
-      <c r="J4" s="51">
-        <v>1</v>
-      </c>
-      <c r="K4" s="54" t="s">
-        <v>130</v>
       </c>
       <c r="L4" s="54"/>
       <c r="M4" s="54"/>
@@ -2705,10 +2381,10 @@
         <v>600</v>
       </c>
       <c r="AL4" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM4" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM4" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN4" s="61">
         <v>500</v>
@@ -2757,9 +2433,9 @@
       </c>
       <c r="BC4" s="48"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:55">
-      <c r="A5" s="51" t="s">
-        <v>133</v>
+    <row r="5" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="65" t="s">
+        <v>238</v>
       </c>
       <c r="B5" s="51" t="s">
         <v>107</v>
@@ -2768,10 +2444,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F5" s="48">
         <v>800</v>
@@ -2779,7 +2455,7 @@
       <c r="G5" s="48"/>
       <c r="H5" s="48"/>
       <c r="I5" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J5" s="51">
         <v>1</v>
@@ -2828,14 +2504,14 @@
         <v>55</v>
       </c>
       <c r="AJ5" s="59">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AK5" s="59"/>
       <c r="AL5" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM5" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM5" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN5" s="61">
         <v>500</v>
@@ -2884,9 +2560,9 @@
       </c>
       <c r="BC5" s="48"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:55">
-      <c r="A6" s="51" t="s">
-        <v>137</v>
+    <row r="6" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="65" t="s">
+        <v>239</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>107</v>
@@ -2895,10 +2571,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F6" s="48">
         <v>800</v>
@@ -2906,7 +2582,7 @@
       <c r="G6" s="48"/>
       <c r="H6" s="48"/>
       <c r="I6" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J6" s="51">
         <v>1</v>
@@ -2959,10 +2635,10 @@
       </c>
       <c r="AK6" s="59"/>
       <c r="AL6" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM6" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM6" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN6" s="61">
         <v>500</v>
@@ -3011,9 +2687,9 @@
       </c>
       <c r="BC6" s="48"/>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:55">
-      <c r="A7" s="51" t="s">
-        <v>138</v>
+    <row r="7" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="65" t="s">
+        <v>240</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>107</v>
@@ -3022,10 +2698,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F7" s="48">
         <v>800</v>
@@ -3033,7 +2709,7 @@
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
       <c r="I7" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J7" s="51">
         <v>1</v>
@@ -3086,10 +2762,10 @@
       </c>
       <c r="AK7" s="59"/>
       <c r="AL7" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM7" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN7" s="61">
         <v>500</v>
@@ -3138,9 +2814,9 @@
       </c>
       <c r="BC7" s="48"/>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:55">
-      <c r="A8" s="51" t="s">
-        <v>140</v>
+    <row r="8" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="65" t="s">
+        <v>241</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>107</v>
@@ -3149,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F8" s="48">
         <v>800</v>
@@ -3160,7 +2836,7 @@
       <c r="G8" s="48"/>
       <c r="H8" s="48"/>
       <c r="I8" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J8" s="51">
         <v>1</v>
@@ -3213,10 +2889,10 @@
       </c>
       <c r="AK8" s="59"/>
       <c r="AL8" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM8" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN8" s="61">
         <v>500</v>
@@ -3265,9 +2941,9 @@
       </c>
       <c r="BC8" s="48"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:55">
-      <c r="A9" s="51" t="s">
-        <v>141</v>
+    <row r="9" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="65" t="s">
+        <v>242</v>
       </c>
       <c r="B9" s="51" t="s">
         <v>107</v>
@@ -3276,10 +2952,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F9" s="48">
         <v>800</v>
@@ -3287,7 +2963,7 @@
       <c r="G9" s="48"/>
       <c r="H9" s="48"/>
       <c r="I9" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J9" s="51">
         <v>1</v>
@@ -3340,10 +3016,10 @@
       </c>
       <c r="AK9" s="59"/>
       <c r="AL9" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM9" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM9" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN9" s="61">
         <v>500</v>
@@ -3392,9 +3068,9 @@
       </c>
       <c r="BC9" s="48"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:55">
-      <c r="A10" s="51" t="s">
-        <v>142</v>
+    <row r="10" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="65" t="s">
+        <v>243</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>107</v>
@@ -3403,10 +3079,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10" s="48">
         <v>800</v>
@@ -3414,7 +3090,7 @@
       <c r="G10" s="48"/>
       <c r="H10" s="48"/>
       <c r="I10" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J10" s="51">
         <v>1</v>
@@ -3467,10 +3143,10 @@
       </c>
       <c r="AK10" s="59"/>
       <c r="AL10" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM10" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM10" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN10" s="61">
         <v>500</v>
@@ -3519,9 +3195,9 @@
       </c>
       <c r="BC10" s="48"/>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:55">
-      <c r="A11" s="51" t="s">
-        <v>143</v>
+    <row r="11" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="65" t="s">
+        <v>244</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>107</v>
@@ -3530,10 +3206,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F11" s="48">
         <v>800</v>
@@ -3541,7 +3217,7 @@
       <c r="G11" s="48"/>
       <c r="H11" s="48"/>
       <c r="I11" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J11" s="51">
         <v>1</v>
@@ -3594,10 +3270,10 @@
       </c>
       <c r="AK11" s="59"/>
       <c r="AL11" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM11" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM11" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN11" s="61">
         <v>500</v>
@@ -3646,9 +3322,9 @@
       </c>
       <c r="BC11" s="48"/>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:55">
-      <c r="A12" s="51" t="s">
-        <v>144</v>
+    <row r="12" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="65" t="s">
+        <v>245</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>107</v>
@@ -3657,10 +3333,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F12" s="48">
         <v>800</v>
@@ -3668,7 +3344,7 @@
       <c r="G12" s="48"/>
       <c r="H12" s="48"/>
       <c r="I12" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J12" s="51">
         <v>1</v>
@@ -3721,10 +3397,10 @@
       </c>
       <c r="AK12" s="59"/>
       <c r="AL12" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM12" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM12" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN12" s="61">
         <v>500</v>
@@ -3773,9 +3449,9 @@
       </c>
       <c r="BC12" s="48"/>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:55">
-      <c r="A13" s="51" t="s">
-        <v>145</v>
+    <row r="13" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="65" t="s">
+        <v>246</v>
       </c>
       <c r="B13" s="51" t="s">
         <v>107</v>
@@ -3784,10 +3460,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F13" s="48">
         <v>800</v>
@@ -3795,7 +3471,7 @@
       <c r="G13" s="48"/>
       <c r="H13" s="48"/>
       <c r="I13" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J13" s="51">
         <v>1</v>
@@ -3848,10 +3524,10 @@
       </c>
       <c r="AK13" s="59"/>
       <c r="AL13" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM13" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM13" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN13" s="61">
         <v>500</v>
@@ -3900,9 +3576,9 @@
       </c>
       <c r="BC13" s="48"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:55">
-      <c r="A14" s="51" t="s">
-        <v>146</v>
+    <row r="14" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="65" t="s">
+        <v>247</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>107</v>
@@ -3911,10 +3587,10 @@
         <v>1</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F14" s="48">
         <v>800</v>
@@ -3922,7 +3598,7 @@
       <c r="G14" s="48"/>
       <c r="H14" s="48"/>
       <c r="I14" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J14" s="51">
         <v>1</v>
@@ -3975,10 +3651,10 @@
       </c>
       <c r="AK14" s="59"/>
       <c r="AL14" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM14" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM14" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN14" s="61">
         <v>500</v>
@@ -4027,9 +3703,9 @@
       </c>
       <c r="BC14" s="48"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:55">
-      <c r="A15" s="51" t="s">
-        <v>147</v>
+    <row r="15" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="65" t="s">
+        <v>248</v>
       </c>
       <c r="B15" s="51" t="s">
         <v>107</v>
@@ -4038,10 +3714,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F15" s="48">
         <v>800</v>
@@ -4049,7 +3725,7 @@
       <c r="G15" s="48"/>
       <c r="H15" s="48"/>
       <c r="I15" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J15" s="51">
         <v>1</v>
@@ -4102,10 +3778,10 @@
       </c>
       <c r="AK15" s="59"/>
       <c r="AL15" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM15" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM15" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN15" s="61">
         <v>500</v>
@@ -4154,9 +3830,9 @@
       </c>
       <c r="BC15" s="48"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:55">
-      <c r="A16" s="51" t="s">
-        <v>148</v>
+    <row r="16" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="65" t="s">
+        <v>249</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>107</v>
@@ -4165,10 +3841,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F16" s="48">
         <v>800</v>
@@ -4176,7 +3852,7 @@
       <c r="G16" s="48"/>
       <c r="H16" s="48"/>
       <c r="I16" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J16" s="51">
         <v>1</v>
@@ -4229,10 +3905,10 @@
       </c>
       <c r="AK16" s="59"/>
       <c r="AL16" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM16" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM16" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN16" s="61">
         <v>500</v>
@@ -4281,9 +3957,9 @@
       </c>
       <c r="BC16" s="48"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:55">
-      <c r="A17" s="51" t="s">
-        <v>149</v>
+    <row r="17" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="65" t="s">
+        <v>250</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>107</v>
@@ -4292,10 +3968,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F17" s="48">
         <v>800</v>
@@ -4303,7 +3979,7 @@
       <c r="G17" s="48"/>
       <c r="H17" s="48"/>
       <c r="I17" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J17" s="51">
         <v>1</v>
@@ -4356,10 +4032,10 @@
       </c>
       <c r="AK17" s="59"/>
       <c r="AL17" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM17" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM17" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN17" s="61">
         <v>500</v>
@@ -4408,9 +4084,9 @@
       </c>
       <c r="BC17" s="48"/>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:55">
-      <c r="A18" s="51" t="s">
-        <v>150</v>
+    <row r="18" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="65" t="s">
+        <v>251</v>
       </c>
       <c r="B18" s="51" t="s">
         <v>107</v>
@@ -4419,10 +4095,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F18" s="48">
         <v>800</v>
@@ -4430,7 +4106,7 @@
       <c r="G18" s="48"/>
       <c r="H18" s="48"/>
       <c r="I18" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J18" s="51">
         <v>1</v>
@@ -4483,10 +4159,10 @@
       </c>
       <c r="AK18" s="59"/>
       <c r="AL18" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM18" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM18" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN18" s="61">
         <v>500</v>
@@ -4535,9 +4211,9 @@
       </c>
       <c r="BC18" s="48"/>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:55">
-      <c r="A19" s="51" t="s">
-        <v>151</v>
+    <row r="19" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="65" t="s">
+        <v>252</v>
       </c>
       <c r="B19" s="51" t="s">
         <v>107</v>
@@ -4546,10 +4222,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F19" s="48">
         <v>800</v>
@@ -4557,7 +4233,7 @@
       <c r="G19" s="48"/>
       <c r="H19" s="48"/>
       <c r="I19" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J19" s="51">
         <v>1</v>
@@ -4610,10 +4286,10 @@
       </c>
       <c r="AK19" s="59"/>
       <c r="AL19" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM19" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN19" s="61">
         <v>500</v>
@@ -4662,9 +4338,9 @@
       </c>
       <c r="BC19" s="48"/>
     </row>
-    <row r="20" s="3" customFormat="1" spans="1:55">
-      <c r="A20" s="51" t="s">
-        <v>152</v>
+    <row r="20" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="65" t="s">
+        <v>253</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>107</v>
@@ -4673,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F20" s="48">
         <v>800</v>
@@ -4684,7 +4360,7 @@
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
       <c r="I20" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J20" s="51">
         <v>1</v>
@@ -4737,10 +4413,10 @@
       </c>
       <c r="AK20" s="59"/>
       <c r="AL20" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM20" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM20" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN20" s="61">
         <v>500</v>
@@ -4789,9 +4465,9 @@
       </c>
       <c r="BC20" s="48"/>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:55">
-      <c r="A21" s="51" t="s">
-        <v>153</v>
+    <row r="21" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="65" t="s">
+        <v>254</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>107</v>
@@ -4800,10 +4476,10 @@
         <v>1</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F21" s="48">
         <v>800</v>
@@ -4811,7 +4487,7 @@
       <c r="G21" s="48"/>
       <c r="H21" s="48"/>
       <c r="I21" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J21" s="51">
         <v>1</v>
@@ -4864,10 +4540,10 @@
       </c>
       <c r="AK21" s="59"/>
       <c r="AL21" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM21" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM21" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN21" s="61">
         <v>500</v>
@@ -4916,9 +4592,9 @@
       </c>
       <c r="BC21" s="48"/>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:55">
-      <c r="A22" s="51" t="s">
-        <v>154</v>
+    <row r="22" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="65" t="s">
+        <v>255</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>107</v>
@@ -4927,10 +4603,10 @@
         <v>1</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F22" s="48">
         <v>800</v>
@@ -4938,7 +4614,7 @@
       <c r="G22" s="48"/>
       <c r="H22" s="48"/>
       <c r="I22" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J22" s="51">
         <v>1</v>
@@ -4991,10 +4667,10 @@
       </c>
       <c r="AK22" s="59"/>
       <c r="AL22" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM22" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN22" s="61">
         <v>500</v>
@@ -5043,9 +4719,9 @@
       </c>
       <c r="BC22" s="48"/>
     </row>
-    <row r="23" s="3" customFormat="1" spans="1:55">
-      <c r="A23" s="51" t="s">
-        <v>155</v>
+    <row r="23" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="65" t="s">
+        <v>256</v>
       </c>
       <c r="B23" s="51" t="s">
         <v>107</v>
@@ -5054,10 +4730,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F23" s="48">
         <v>800</v>
@@ -5065,7 +4741,7 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J23" s="51">
         <v>1</v>
@@ -5118,10 +4794,10 @@
       </c>
       <c r="AK23" s="59"/>
       <c r="AL23" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM23" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN23" s="61">
         <v>500</v>
@@ -5170,9 +4846,9 @@
       </c>
       <c r="BC23" s="48"/>
     </row>
-    <row r="24" s="3" customFormat="1" spans="1:55">
-      <c r="A24" s="51" t="s">
-        <v>156</v>
+    <row r="24" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="65" t="s">
+        <v>257</v>
       </c>
       <c r="B24" s="51" t="s">
         <v>107</v>
@@ -5181,10 +4857,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F24" s="48">
         <v>800</v>
@@ -5192,7 +4868,7 @@
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
       <c r="I24" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J24" s="51">
         <v>1</v>
@@ -5245,10 +4921,10 @@
       </c>
       <c r="AK24" s="59"/>
       <c r="AL24" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM24" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN24" s="61">
         <v>500</v>
@@ -5297,9 +4973,9 @@
       </c>
       <c r="BC24" s="48"/>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:55">
-      <c r="A25" s="51" t="s">
-        <v>157</v>
+    <row r="25" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="65" t="s">
+        <v>258</v>
       </c>
       <c r="B25" s="51" t="s">
         <v>107</v>
@@ -5308,10 +4984,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F25" s="48">
         <v>800</v>
@@ -5319,7 +4995,7 @@
       <c r="G25" s="48"/>
       <c r="H25" s="48"/>
       <c r="I25" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J25" s="51">
         <v>1</v>
@@ -5372,10 +5048,10 @@
       </c>
       <c r="AK25" s="59"/>
       <c r="AL25" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM25" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN25" s="61">
         <v>500</v>
@@ -5424,9 +5100,9 @@
       </c>
       <c r="BC25" s="48"/>
     </row>
-    <row r="26" s="3" customFormat="1" spans="1:55">
-      <c r="A26" s="51" t="s">
-        <v>158</v>
+    <row r="26" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="65" t="s">
+        <v>259</v>
       </c>
       <c r="B26" s="51" t="s">
         <v>107</v>
@@ -5435,10 +5111,10 @@
         <v>1</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F26" s="48">
         <v>800</v>
@@ -5446,7 +5122,7 @@
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
       <c r="I26" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J26" s="51">
         <v>1</v>
@@ -5499,10 +5175,10 @@
       </c>
       <c r="AK26" s="59"/>
       <c r="AL26" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM26" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM26" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN26" s="61">
         <v>500</v>
@@ -5551,9 +5227,9 @@
       </c>
       <c r="BC26" s="48"/>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:55">
-      <c r="A27" s="51" t="s">
-        <v>159</v>
+    <row r="27" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="65" t="s">
+        <v>260</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>107</v>
@@ -5562,10 +5238,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F27" s="48">
         <v>800</v>
@@ -5573,7 +5249,7 @@
       <c r="G27" s="48"/>
       <c r="H27" s="48"/>
       <c r="I27" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J27" s="51">
         <v>1</v>
@@ -5626,10 +5302,10 @@
       </c>
       <c r="AK27" s="59"/>
       <c r="AL27" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM27" s="61" t="s">
         <v>131</v>
-      </c>
-      <c r="AM27" s="61" t="s">
-        <v>132</v>
       </c>
       <c r="AN27" s="61">
         <v>500</v>
@@ -5678,9 +5354,9 @@
       </c>
       <c r="BC27" s="48"/>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:55">
-      <c r="A28" s="51" t="s">
-        <v>160</v>
+    <row r="28" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="65" t="s">
+        <v>261</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>107</v>
@@ -5689,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F28" s="48">
         <v>800</v>
@@ -5700,7 +5376,7 @@
       <c r="G28" s="48"/>
       <c r="H28" s="48"/>
       <c r="I28" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J28" s="51">
         <v>1</v>
@@ -5753,10 +5429,10 @@
       </c>
       <c r="AK28" s="59"/>
       <c r="AL28" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM28" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN28" s="61">
         <v>500</v>
@@ -5805,9 +5481,9 @@
       </c>
       <c r="BC28" s="48"/>
     </row>
-    <row r="29" s="3" customFormat="1" spans="1:55">
-      <c r="A29" s="51" t="s">
-        <v>161</v>
+    <row r="29" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="65" t="s">
+        <v>262</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>107</v>
@@ -5816,10 +5492,10 @@
         <v>1</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F29" s="48">
         <v>800</v>
@@ -5827,7 +5503,7 @@
       <c r="G29" s="48"/>
       <c r="H29" s="48"/>
       <c r="I29" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J29" s="51">
         <v>1</v>
@@ -5880,10 +5556,10 @@
       </c>
       <c r="AK29" s="59"/>
       <c r="AL29" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM29" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN29" s="61">
         <v>500</v>
@@ -5932,9 +5608,9 @@
       </c>
       <c r="BC29" s="48"/>
     </row>
-    <row r="30" s="3" customFormat="1" spans="1:55">
-      <c r="A30" s="51" t="s">
-        <v>162</v>
+    <row r="30" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="65" t="s">
+        <v>263</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>107</v>
@@ -5943,10 +5619,10 @@
         <v>1</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F30" s="48">
         <v>800</v>
@@ -5954,7 +5630,7 @@
       <c r="G30" s="48"/>
       <c r="H30" s="48"/>
       <c r="I30" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J30" s="51">
         <v>1</v>
@@ -6007,10 +5683,10 @@
       </c>
       <c r="AK30" s="59"/>
       <c r="AL30" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM30" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN30" s="61">
         <v>500</v>
@@ -6059,9 +5735,9 @@
       </c>
       <c r="BC30" s="48"/>
     </row>
-    <row r="31" s="3" customFormat="1" spans="1:55">
-      <c r="A31" s="51" t="s">
-        <v>163</v>
+    <row r="31" spans="1:55" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="65" t="s">
+        <v>264</v>
       </c>
       <c r="B31" s="51" t="s">
         <v>107</v>
@@ -6070,10 +5746,10 @@
         <v>1</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F31" s="48">
         <v>800</v>
@@ -6081,7 +5757,7 @@
       <c r="G31" s="48"/>
       <c r="H31" s="48"/>
       <c r="I31" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J31" s="51">
         <v>1</v>
@@ -6134,10 +5810,10 @@
       </c>
       <c r="AK31" s="59"/>
       <c r="AL31" s="61" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AM31" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AN31" s="61">
         <v>500</v>
@@ -6187,39 +5863,38 @@
       <c r="BC31" s="48"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.1416666666667" customWidth="1"/>
-    <col min="2" max="2" width="12.425" customWidth="1"/>
-    <col min="3" max="3" width="31.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="39.3583333333333" customWidth="1"/>
+    <col min="1" max="1" width="29.125" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="31.25" customWidth="1"/>
+    <col min="4" max="4" width="39.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
         <v>53</v>
       </c>
@@ -6231,31 +5906,31 @@
       </c>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
       </c>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
         <v>80</v>
       </c>
@@ -6267,19 +5942,19 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
         <v>81</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
       </c>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
         <v>82</v>
       </c>
@@ -6291,19 +5966,19 @@
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
         <v>84</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3">
         <v>3</v>
       </c>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="35" t="s">
         <v>83</v>
       </c>
@@ -6315,7 +5990,7 @@
       </c>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="35" t="s">
         <v>78</v>
       </c>
@@ -6327,7 +6002,7 @@
       </c>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="35" t="s">
         <v>79</v>
       </c>
@@ -6339,7 +6014,7 @@
       </c>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="35" t="s">
         <v>89</v>
       </c>
@@ -6347,13 +6022,13 @@
         <v>37</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="35" t="s">
         <v>86</v>
       </c>
@@ -6365,7 +6040,7 @@
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="35" t="s">
         <v>85</v>
       </c>
@@ -6377,19 +6052,19 @@
       </c>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="35" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="C15" s="3">
         <v>110</v>
       </c>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="35" t="s">
         <v>87</v>
       </c>
@@ -6401,7 +6076,7 @@
       </c>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="35" t="s">
         <v>88</v>
       </c>
@@ -6413,55 +6088,55 @@
       </c>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="35" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="C18" s="3">
         <v>900</v>
       </c>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="35" t="s">
         <v>56</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="34" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
         <v>57</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="C20" s="3">
         <v>1000</v>
       </c>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="35" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="C21" s="3">
         <v>0.3</v>
       </c>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
         <v>90</v>
       </c>
@@ -6469,13 +6144,13 @@
         <v>38</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="35" t="s">
         <v>91</v>
       </c>
@@ -6487,195 +6162,195 @@
       </c>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="35" t="s">
         <v>92</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="35" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3">
         <v>1200</v>
       </c>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="35" t="s">
         <v>98</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3">
         <v>1000</v>
       </c>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="35" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="C27" s="3">
         <v>50</v>
       </c>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="35" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C28" s="3">
         <v>40</v>
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="35" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="C29" s="3">
         <v>20</v>
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="35" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="35" t="s">
         <v>102</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
       </c>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="37" t="s">
         <v>105</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="34" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="35" t="s">
         <v>103</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="35" t="s">
         <v>101</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="35" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="35" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="35" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="35" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="35" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="35" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="35" t="s">
         <v>99</v>
       </c>
@@ -6685,7 +6360,7 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="35" t="s">
         <v>100</v>
       </c>
@@ -6695,59 +6370,59 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="35" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="35" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="35" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="35" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="35" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="35" t="s">
         <v>55</v>
       </c>
@@ -6757,7 +6432,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="35" t="s">
         <v>61</v>
       </c>
@@ -6767,86 +6442,85 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="35" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="35" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BE19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.1416666666667" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26.6416666666667" style="4" customWidth="1"/>
-    <col min="3" max="3" width="3.70833333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.0666666666667" customWidth="1"/>
-    <col min="5" max="5" width="18.8583333333333" style="4" customWidth="1"/>
-    <col min="6" max="6" width="5.06666666666667" style="4" customWidth="1"/>
-    <col min="7" max="7" width="5.925" style="5" customWidth="1"/>
-    <col min="8" max="8" width="5.35833333333333" customWidth="1"/>
-    <col min="9" max="9" width="7.35833333333333" customWidth="1"/>
-    <col min="10" max="21" width="5.35833333333333" customWidth="1"/>
-    <col min="22" max="22" width="10.0666666666667" customWidth="1"/>
-    <col min="23" max="23" width="40.3583333333333" customWidth="1"/>
-    <col min="24" max="24" width="20.0666666666667" style="6" customWidth="1"/>
-    <col min="25" max="25" width="13.8583333333333" customWidth="1"/>
-    <col min="26" max="26" width="29.8583333333333" customWidth="1"/>
-    <col min="27" max="27" width="25.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="31.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="26.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="3.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="5.125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="5.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="5.375" customWidth="1"/>
+    <col min="9" max="9" width="7.375" customWidth="1"/>
+    <col min="10" max="21" width="5.375" customWidth="1"/>
+    <col min="22" max="22" width="10.125" customWidth="1"/>
+    <col min="23" max="23" width="40.375" customWidth="1"/>
+    <col min="24" max="24" width="20.125" style="6" customWidth="1"/>
+    <col min="25" max="25" width="13.875" customWidth="1"/>
+    <col min="26" max="26" width="29.875" customWidth="1"/>
+    <col min="27" max="27" width="25.125" customWidth="1"/>
     <col min="28" max="28" width="23" customWidth="1"/>
-    <col min="29" max="29" width="27.0666666666667" customWidth="1"/>
-    <col min="30" max="30" width="29.6416666666667" customWidth="1"/>
-    <col min="31" max="31" width="28.425" customWidth="1"/>
-    <col min="32" max="32" width="10.3583333333333" style="5" customWidth="1"/>
-    <col min="33" max="33" width="6.85833333333333" style="7" customWidth="1"/>
-    <col min="34" max="34" width="6.85833333333333" style="5" customWidth="1"/>
-    <col min="35" max="35" width="6.85833333333333" style="8" customWidth="1"/>
+    <col min="29" max="29" width="27.125" customWidth="1"/>
+    <col min="30" max="30" width="29.625" customWidth="1"/>
+    <col min="31" max="31" width="28.375" customWidth="1"/>
+    <col min="32" max="32" width="10.375" style="5" customWidth="1"/>
+    <col min="33" max="33" width="6.875" style="7" customWidth="1"/>
+    <col min="34" max="34" width="6.875" style="5" customWidth="1"/>
+    <col min="35" max="35" width="6.875" style="8" customWidth="1"/>
     <col min="36" max="36" width="21" style="5" customWidth="1"/>
-    <col min="37" max="37" width="20.3583333333333" style="5" customWidth="1"/>
-    <col min="38" max="38" width="30.8583333333333" style="5" customWidth="1"/>
-    <col min="39" max="46" width="6.85833333333333" style="5" customWidth="1"/>
-    <col min="47" max="47" width="5.06666666666667" style="5" customWidth="1"/>
-    <col min="48" max="48" width="5.925" style="5" customWidth="1"/>
-    <col min="49" max="51" width="6.85833333333333" style="5" customWidth="1"/>
-    <col min="52" max="52" width="22.925" style="5" customWidth="1"/>
-    <col min="53" max="53" width="6.85833333333333" style="5" customWidth="1"/>
-    <col min="54" max="54" width="24.0666666666667" customWidth="1"/>
-    <col min="55" max="55" width="12.0666666666667" customWidth="1"/>
-    <col min="56" max="56" width="20.8583333333333" customWidth="1"/>
+    <col min="37" max="37" width="20.375" style="5" customWidth="1"/>
+    <col min="38" max="38" width="30.875" style="5" customWidth="1"/>
+    <col min="39" max="46" width="6.875" style="5" customWidth="1"/>
+    <col min="47" max="47" width="5.125" style="5" customWidth="1"/>
+    <col min="48" max="48" width="5.875" style="5" customWidth="1"/>
+    <col min="49" max="51" width="6.875" style="5" customWidth="1"/>
+    <col min="52" max="52" width="22.875" style="5" customWidth="1"/>
+    <col min="53" max="53" width="6.875" style="5" customWidth="1"/>
+    <col min="54" max="54" width="24.125" customWidth="1"/>
+    <col min="55" max="55" width="12.125" customWidth="1"/>
+    <col min="56" max="56" width="20.875" customWidth="1"/>
     <col min="57" max="57" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31.5" customHeight="1" spans="1:57">
+    <row r="1" spans="1:57" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>1</v>
@@ -6855,16 +6529,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
@@ -6879,16 +6553,16 @@
       <c r="T1" s="12"/>
       <c r="U1" s="12"/>
       <c r="V1" s="12" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="W1" s="12" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="X1" s="17" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
@@ -6897,28 +6571,28 @@
       <c r="AD1" s="20"/>
       <c r="AE1" s="20"/>
       <c r="AF1" s="20" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="AG1" s="23" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="AH1" s="10" t="s">
         <v>39</v>
       </c>
       <c r="AI1" s="24" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="AJ1" s="25" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="AK1" s="10" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="AL1" s="26" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="10" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="AN1" s="10" t="s">
         <v>27</v>
@@ -6927,57 +6601,57 @@
         <v>28</v>
       </c>
       <c r="AP1" s="10" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="AQ1" s="10" t="s">
         <v>30</v>
       </c>
       <c r="AR1" s="10" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="AS1" s="10" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="AT1" s="10" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="AU1" s="26" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="AV1" s="26" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="AW1" s="26" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="AX1" s="32" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="AY1" s="26" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="AZ1" s="26" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="BA1" s="26" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="BB1" s="33" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="BC1" s="33" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="BD1" s="33" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="BE1" s="33" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="36.75" customHeight="1" spans="1:57">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" s="1" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -6988,16 +6662,16 @@
         <v>55</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>61</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="J2" s="12">
         <v>1</v>
@@ -7030,22 +6704,22 @@
         <v>10</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="V2" s="12" t="s">
         <v>59</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="X2" s="17" t="s">
         <v>60</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="Z2" s="20" t="s">
         <v>62</v>
@@ -7078,7 +6752,7 @@
         <v>92</v>
       </c>
       <c r="AJ2" s="25" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="AK2" s="10" t="s">
         <v>90</v>
@@ -7105,10 +6779,10 @@
         <v>84</v>
       </c>
       <c r="AS2" s="10" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="AT2" s="10" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="AU2" s="26" t="s">
         <v>85</v>
@@ -7126,7 +6800,7 @@
         <v>88</v>
       </c>
       <c r="AZ2" s="26" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>104</v>
@@ -7138,18 +6812,18 @@
         <v>57</v>
       </c>
       <c r="BD2" s="33" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="BE2" s="33" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:57">
+    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C3" s="13" t="str">
         <f>SUBSTITUTE(B3,"npc_dota_hero_","")</f>
@@ -7159,7 +6833,7 @@
         <v>107</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="14">
@@ -7184,14 +6858,14 @@
       <c r="T3" s="14"/>
       <c r="U3" s="14"/>
       <c r="V3" s="14" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="W3" s="14"/>
       <c r="X3" s="18" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="Y3" s="18" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="Z3" s="21"/>
       <c r="AA3" s="18"/>
@@ -7218,7 +6892,7 @@
         <v>#REF!</v>
       </c>
       <c r="AK3" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AL3" s="18" t="e">
         <f>VLOOKUP("npc_dota_hero_"&amp;$C3,#REF!,19,FALSE)</f>
@@ -7264,7 +6938,7 @@
         <v>130</v>
       </c>
       <c r="AZ3" s="18" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="BA3" s="14">
         <v>70</v>
@@ -7275,7 +6949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:53">
+    <row r="4" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -7306,7 +6980,7 @@
       <c r="AZ4" s="16"/>
       <c r="BA4" s="16"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:53">
+    <row r="5" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -7337,7 +7011,7 @@
       <c r="AZ5" s="16"/>
       <c r="BA5" s="16"/>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:53">
+    <row r="6" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -7368,7 +7042,7 @@
       <c r="AZ6" s="16"/>
       <c r="BA6" s="16"/>
     </row>
-    <row r="7" s="3" customFormat="1" spans="1:53">
+    <row r="7" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -7399,7 +7073,7 @@
       <c r="AZ7" s="16"/>
       <c r="BA7" s="16"/>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:53">
+    <row r="8" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -7430,7 +7104,7 @@
       <c r="AZ8" s="16"/>
       <c r="BA8" s="16"/>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:53">
+    <row r="9" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -7461,7 +7135,7 @@
       <c r="AZ9" s="16"/>
       <c r="BA9" s="16"/>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:53">
+    <row r="10" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -7492,7 +7166,7 @@
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16"/>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:53">
+    <row r="11" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -7523,7 +7197,7 @@
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16"/>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:53">
+    <row r="12" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -7554,7 +7228,7 @@
       <c r="AZ12" s="16"/>
       <c r="BA12" s="16"/>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:53">
+    <row r="13" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -7585,7 +7259,7 @@
       <c r="AZ13" s="16"/>
       <c r="BA13" s="16"/>
     </row>
-    <row r="14" s="3" customFormat="1" spans="1:53">
+    <row r="14" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -7616,7 +7290,7 @@
       <c r="AZ14" s="16"/>
       <c r="BA14" s="16"/>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:53">
+    <row r="15" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -7647,7 +7321,7 @@
       <c r="AZ15" s="16"/>
       <c r="BA15" s="16"/>
     </row>
-    <row r="16" s="3" customFormat="1" spans="1:53">
+    <row r="16" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -7678,7 +7352,7 @@
       <c r="AZ16" s="16"/>
       <c r="BA16" s="16"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:53">
+    <row r="17" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -7709,7 +7383,7 @@
       <c r="AZ17" s="16"/>
       <c r="BA17" s="16"/>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:53">
+    <row r="18" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -7740,7 +7414,7 @@
       <c r="AZ18" s="16"/>
       <c r="BA18" s="16"/>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:53">
+    <row r="19" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -7772,172 +7446,172 @@
       <c r="BA19" s="16"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="containsText" dxfId="0" priority="38" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="38" priority="38" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3">
-    <cfRule type="containsText" dxfId="0" priority="35" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="37" priority="35" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",W3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3">
-    <cfRule type="containsText" dxfId="0" priority="36" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="36" priority="36" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",X3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3:AA3">
-    <cfRule type="containsText" dxfId="0" priority="33" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="35" priority="33" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",Y3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
-    <cfRule type="containsText" dxfId="0" priority="7" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="34" priority="7" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AA3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB3">
-    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="33" priority="10" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD3:AE3">
-    <cfRule type="containsText" dxfId="0" priority="6" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG3">
-    <cfRule type="containsText" dxfId="0" priority="32" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="31" priority="32" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AG3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH3">
-    <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="30" priority="31" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI3">
-    <cfRule type="containsText" dxfId="0" priority="30" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="29" priority="30" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AI3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3">
-    <cfRule type="containsText" dxfId="0" priority="29" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="28" priority="29" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AJ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3">
-    <cfRule type="containsText" dxfId="0" priority="28" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="27" priority="28" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AK3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL3">
-    <cfRule type="containsText" dxfId="0" priority="27" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AL3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW3">
-    <cfRule type="containsBlanks" dxfId="1" priority="37">
+    <cfRule type="containsBlanks" dxfId="25" priority="37">
       <formula>LEN(TRIM(AW3))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="14" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+    <cfRule type="containsText" dxfId="24" priority="14" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",AW3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="13" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="23" priority="13" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",AW3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="12" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="22" priority="12" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AW3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX3">
-    <cfRule type="containsText" dxfId="2" priority="26" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+    <cfRule type="containsText" dxfId="21" priority="26" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",AX3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="25" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="20" priority="25" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",AX3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="24" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AX3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY3">
-    <cfRule type="containsText" dxfId="2" priority="23" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",AY3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="22" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="17" priority="22" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",AY3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="21" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="16" priority="21" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AY3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="15" priority="5">
       <formula>$AL3="DOTA_UNIT_CAP_RANGED_ATTACK"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+    <cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",AZ3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",AZ3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB3">
-    <cfRule type="containsText" dxfId="2" priority="20" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",BB3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="19" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",BB3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="9" priority="18" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",BB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC3">
-    <cfRule type="containsText" dxfId="2" priority="17" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",BC3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="16" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",BC3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",BC3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL$1:AL$1048576">
-    <cfRule type="containsText" dxfId="2" priority="9" operator="between" text="DOTA_UNIT_CAP_RANGED_ATTACK">
+  <conditionalFormatting sqref="AL1:AL1048576">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="DOTA_UNIT_CAP_RANGED_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_RANGED_ATTACK",AL1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="8" operator="between" text="DOTA_UNIT_CAP_MELEE_ATTACK">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="DOTA_UNIT_CAP_MELEE_ATTACK">
       <formula>NOT(ISERROR(SEARCH("DOTA_UNIT_CAP_MELEE_ATTACK",AL1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY1:BC2">
-    <cfRule type="expression" dxfId="4" priority="39">
+    <cfRule type="expression" dxfId="3" priority="39">
       <formula>$AL1="DOTA_UNIT_CAP_RANGED_ATTACK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD1:BE2">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$AL1="DOTA_UNIT_CAP_RANGED_ATTACK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V3 A3:C3">
-    <cfRule type="containsText" dxfId="0" priority="34" operator="between" text="_custom">
+    <cfRule type="containsText" dxfId="1" priority="34" operator="containsText" text="_custom">
       <formula>NOT(ISERROR(SEARCH("_custom",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:AB3 AY4:BC1048576 AD3:AY3 A3:I3 BA3:XFD3">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>$AL3="DOTA_UNIT_CAP_RANGED_ATTACK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>